--- a/planner_tasks_consolidated.xlsx
+++ b/planner_tasks_consolidated.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30610"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="13980" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB747B8D-42FF-41F6-B57E-62F7C81582B4}"/>
+  <xr:revisionPtr revIDLastSave="14444" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D632CB7-7067-4810-B8B2-61979B28BAB7}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="988">
   <si>
     <t>RunTimestamp</t>
   </si>
@@ -143,7 +143,7 @@
     <t>DaysToDue</t>
   </si>
   <si>
-    <t>2026-10-14T08:29:31.9025982Z</t>
+    <t>2026-10-14T12:29:11.3602106Z</t>
   </si>
   <si>
     <t>8PerGupe7k-8TC9qFcKmxmQAGnQG</t>
@@ -191,7 +191,7 @@
     <t>Coupa PO</t>
   </si>
   <si>
-    <t>2026-10-14T08:29:34.9668433Z</t>
+    <t>2026-10-14T12:29:13.6798789Z</t>
   </si>
   <si>
     <t>KOLwYhtXk0yf0oNg5Z1fBWQADn__</t>
@@ -215,7 +215,7 @@
     <t>LinkedIn, Facebook</t>
   </si>
   <si>
-    <t>2026-10-14T08:29:37.8595326Z</t>
+    <t>2026-10-14T12:29:16.2749402Z</t>
   </si>
   <si>
     <t>TpTTzdxeCUqrFSMT4LL2HmQAGLVV</t>
@@ -224,213 +224,219 @@
     <t>Create Nurture email in Japanese</t>
   </si>
   <si>
+    <t>hXWXxcacR0e8OSPDfuHME2QAMCsP</t>
+  </si>
+  <si>
+    <t>Next Week</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-14T07:51:55.8318815Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"8021679b-08c3-4b58-beef-284f1a8378ef"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-14T07:51:55.8319336Z</t>
+  </si>
+  <si>
+    <t>8021679b-08c3-4b58-beef-284f1a8378ef</t>
+  </si>
+  <si>
+    <t>2026-10-23T10:00:00Z</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1HU50GjvMv0_Y5PinSOHZQjJ17hTKHI_X5y-hgeT905s/edit?gid=0#gid=0</t>
+  </si>
+  <si>
+    <t>8584096426296966342P/</t>
+  </si>
+  <si>
+    <t>Aisah Abdul Talib</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:19.1069284Z</t>
+  </si>
+  <si>
+    <t>cvVWGTY-x0Kx5TCslWRiHGQAGVOB</t>
+  </si>
+  <si>
+    <t>Include the 10k budget accordingly in the plan</t>
+  </si>
+  <si>
+    <t>FcWT8p45_0yAmU3I_Ewh9GQAGRCc</t>
+  </si>
+  <si>
+    <t>Doing Now</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-14T07:48:31.3336222Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-14T07:48:31.3336828Z</t>
+  </si>
+  <si>
+    <t>{"category11":true}</t>
+  </si>
+  <si>
+    <t>8584096428341945920P+</t>
+  </si>
+  <si>
+    <t>ADS- Planning</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:22.7100757Z</t>
+  </si>
+  <si>
+    <t>Wtp28rCL9EKmajHdYOY332QAEN3D</t>
+  </si>
+  <si>
+    <t>Include exclusion for all campaigns</t>
+  </si>
+  <si>
+    <t>VvFb0U6zYUiz9zKudbSK6WQAP0Yz</t>
+  </si>
+  <si>
+    <t>This Week</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-13T08:03:19.7677405Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-13T08:03:19.7678053Z</t>
+  </si>
+  <si>
+    <t>{"category11":true,"category19":true,"category20":true}</t>
+  </si>
+  <si>
+    <t>8584097283458834685P"</t>
+  </si>
+  <si>
+    <t>ADS- Planning, LinkedIn, Facebook</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:24.8709820Z</t>
+  </si>
+  <si>
+    <t>JTT4t0X7wEKBlTRGx7tqumQAIFkY</t>
+  </si>
+  <si>
+    <t>Fix disabled Power Automate flow (BrandCom task completion)</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T11:42:36.0988305Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-12T11:42:10.2049716Z</t>
+  </si>
+  <si>
+    <t>129b8133-2f40-46f4-8391-49fec10f3174</t>
+  </si>
+  <si>
+    <t>{"category15":true}</t>
+  </si>
+  <si>
+    <t>[{"id":"88bb571560fc460d85ac5aa56abf03ef","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Re-enable the flow","orderHint":"8584098014G*","lastModifiedDateTime":"2026-10-12T11:43:57.3149744Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1faab196a14949ed8dfb00ad34cc820b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Fix the failing step or connection","orderHint":"8584098014Z=","lastModifiedDateTime":"2026-10-12T11:43:45.2923942Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"e854660ebc064eb3970c23341ff7a336","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Test with a completed BrandCom task","orderHint":"8584098014=-","lastModifiedDateTime":"2026-10-12T11:44:06.2121252Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"6a72e1a1253342b090686782cc2a2288","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Open the failed flow run history to find the error","orderHint":"8584098015320168408PD","lastModifiedDateTime":"2026-10-12T11:43:33.4849961Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584098016153157541P?</t>
+  </si>
+  <si>
+    <t>Adam Lau</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:27.9791434Z</t>
+  </si>
+  <si>
+    <t>TPlkTO8EW0C-8c5GaD8rHmQADZ2R</t>
+  </si>
+  <si>
+    <t>EMEA-style campaign heads-up to sales</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T11:32:55.4815343Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-12T11:30:20.1384934Z</t>
+  </si>
+  <si>
+    <t>[{"id":"eb6f6a79c9514ea7add5654fe76f260c","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Pull the campaign details sales actually needs","orderHint":"85840980165M","lastModifiedDateTime":"2026-10-12T11:41:11.0090546Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"e7ba75c0c99c4988a442b7c3a167b28b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft the heads-up format/template","orderHint":"85840980162C","lastModifiedDateTime":"2026-10-12T11:41:21.5551439Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"65f9351d878140b3af6283a98c3839d5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Send the first heads-up for current campaigns","orderHint":"8584098015IB","lastModifiedDateTime":"2026-10-12T11:41:43.316013Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"aca24e12ec654b8da406dc0d5188b082","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm where it lives (Salesforce, email, or Teams)","orderHint":"8584098015[O","lastModifiedDateTime":"2026-10-12T11:41:36.707008Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ddde352ea9384a5487e60eae1b69b285","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Clarify with Michelle what EMEA's sales heads-up contains","orderHint":"8584098016918080319P4","lastModifiedDateTime":"2026-10-12T11:40:53.6861529Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584098023254005852P3</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:30.1525523Z</t>
+  </si>
+  <si>
+    <t>TbJUsV4QykaPI10fcdCem2QAH-mt</t>
+  </si>
+  <si>
+    <t>Update budget tracker with approved budget</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T07:23:59.0601835Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-12T07:23:59.0602437Z</t>
+  </si>
+  <si>
+    <t>8584098171064541296P'</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:32.6651716Z</t>
+  </si>
+  <si>
+    <t>v6s3jGKO5UuqjkWZsylQ12QANSnd</t>
+  </si>
+  <si>
+    <t>Share the final budget with each market manager</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T07:23:42.6024867Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-12T07:23:42.6025502Z</t>
+  </si>
+  <si>
+    <t>8584098171229149186P7</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:35.3166872Z</t>
+  </si>
+  <si>
+    <t>YIb6OiUp6E-GVU6YdOb4jGQAKmPu</t>
+  </si>
+  <si>
+    <t>Get final approval for media plan budgets</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T07:23:29.870497Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-12T07:23:29.8705559Z</t>
+  </si>
+  <si>
+    <t>8584098171357006846P/</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:29:38.0142120Z</t>
+  </si>
+  <si>
+    <t>Er2oCUuoCkKX8CAjW5UE4GQAKaCr</t>
+  </si>
+  <si>
+    <t>Add New Audience to target (Hidden audience - Office managers, team mgrs)</t>
+  </si>
+  <si>
     <t>f1v-2jW3aU-0dIkZTM4BkGQAEhcr</t>
   </si>
   <si>
     <t>[Inbox]</t>
   </si>
   <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-14T07:51:55.8318815Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"8021679b-08c3-4b58-beef-284f1a8378ef"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-14T07:51:55.8319336Z</t>
-  </si>
-  <si>
-    <t>8021679b-08c3-4b58-beef-284f1a8378ef</t>
-  </si>
-  <si>
-    <t>2026-10-23T10:00:00Z</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1HU50GjvMv0_Y5PinSOHZQjJ17hTKHI_X5y-hgeT905s/edit?gid=0#gid=0</t>
-  </si>
-  <si>
-    <t>8584096426296966342P/</t>
-  </si>
-  <si>
-    <t>Aisah Abdul Talib</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:40.1682914Z</t>
-  </si>
-  <si>
-    <t>cvVWGTY-x0Kx5TCslWRiHGQAGVOB</t>
-  </si>
-  <si>
-    <t>Include the 10k budget accordingly in the plan</t>
-  </si>
-  <si>
-    <t>FcWT8p45_0yAmU3I_Ewh9GQAGRCc</t>
-  </si>
-  <si>
-    <t>Doing Now</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-14T07:48:31.3336222Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-14T07:48:31.3336828Z</t>
-  </si>
-  <si>
-    <t>{"category11":true}</t>
-  </si>
-  <si>
-    <t>8584096428341945920P+</t>
-  </si>
-  <si>
-    <t>ADS- Planning</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:42.6250247Z</t>
-  </si>
-  <si>
-    <t>Wtp28rCL9EKmajHdYOY332QAEN3D</t>
-  </si>
-  <si>
-    <t>Include exclusion for all campaigns</t>
-  </si>
-  <si>
-    <t>VvFb0U6zYUiz9zKudbSK6WQAP0Yz</t>
-  </si>
-  <si>
-    <t>This Week</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-13T08:03:19.7677405Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-13T08:03:19.7678053Z</t>
-  </si>
-  <si>
-    <t>{"category11":true,"category19":true,"category20":true}</t>
-  </si>
-  <si>
-    <t>8584097283458834685P"</t>
-  </si>
-  <si>
-    <t>ADS- Planning, LinkedIn, Facebook</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:45.1873377Z</t>
-  </si>
-  <si>
-    <t>JTT4t0X7wEKBlTRGx7tqumQAIFkY</t>
-  </si>
-  <si>
-    <t>Fix disabled Power Automate flow (BrandCom task completion)</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T11:42:36.0988305Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-12T11:42:10.2049716Z</t>
-  </si>
-  <si>
-    <t>129b8133-2f40-46f4-8391-49fec10f3174</t>
-  </si>
-  <si>
-    <t>{"category15":true}</t>
-  </si>
-  <si>
-    <t>[{"id":"88bb571560fc460d85ac5aa56abf03ef","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Re-enable the flow","orderHint":"8584098014G*","lastModifiedDateTime":"2026-10-12T11:43:57.3149744Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1faab196a14949ed8dfb00ad34cc820b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Fix the failing step or connection","orderHint":"8584098014Z=","lastModifiedDateTime":"2026-10-12T11:43:45.2923942Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"e854660ebc064eb3970c23341ff7a336","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Test with a completed BrandCom task","orderHint":"8584098014=-","lastModifiedDateTime":"2026-10-12T11:44:06.2121252Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"6a72e1a1253342b090686782cc2a2288","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Open the failed flow run history to find the error","orderHint":"8584098015320168408PD","lastModifiedDateTime":"2026-10-12T11:43:33.4849961Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584098016153157541P?</t>
-  </si>
-  <si>
-    <t>Adam Lau</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:48.2842313Z</t>
-  </si>
-  <si>
-    <t>TPlkTO8EW0C-8c5GaD8rHmQADZ2R</t>
-  </si>
-  <si>
-    <t>EMEA-style campaign heads-up to sales</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T11:32:55.4815343Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-12T11:30:20.1384934Z</t>
-  </si>
-  <si>
-    <t>[{"id":"eb6f6a79c9514ea7add5654fe76f260c","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Pull the campaign details sales actually needs","orderHint":"85840980165M","lastModifiedDateTime":"2026-10-12T11:41:11.0090546Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"e7ba75c0c99c4988a442b7c3a167b28b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft the heads-up format/template","orderHint":"85840980162C","lastModifiedDateTime":"2026-10-12T11:41:21.5551439Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"65f9351d878140b3af6283a98c3839d5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Send the first heads-up for current campaigns","orderHint":"8584098015IB","lastModifiedDateTime":"2026-10-12T11:41:43.316013Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"aca24e12ec654b8da406dc0d5188b082","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm where it lives (Salesforce, email, or Teams)","orderHint":"8584098015[O","lastModifiedDateTime":"2026-10-12T11:41:36.707008Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ddde352ea9384a5487e60eae1b69b285","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Clarify with Michelle what EMEA's sales heads-up contains","orderHint":"8584098016918080319P4","lastModifiedDateTime":"2026-10-12T11:40:53.6861529Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584098023254005852P3</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:51.1355961Z</t>
-  </si>
-  <si>
-    <t>TbJUsV4QykaPI10fcdCem2QAH-mt</t>
-  </si>
-  <si>
-    <t>Update budget tracker with approved budget</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T07:23:59.0601835Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-12T07:23:59.0602437Z</t>
-  </si>
-  <si>
-    <t>8584098171064541296P'</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:53.9054776Z</t>
-  </si>
-  <si>
-    <t>v6s3jGKO5UuqjkWZsylQ12QANSnd</t>
-  </si>
-  <si>
-    <t>Share the final budget with each market manager</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T07:23:42.6024867Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-12T07:23:42.6025502Z</t>
-  </si>
-  <si>
-    <t>8584098171229149186P7</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:56.3475615Z</t>
-  </si>
-  <si>
-    <t>YIb6OiUp6E-GVU6YdOb4jGQAKmPu</t>
-  </si>
-  <si>
-    <t>Get final approval for media plan budgets</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T07:23:29.870497Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-12T07:23:29.8705559Z</t>
-  </si>
-  <si>
-    <t>8584098171357006846P/</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:29:58.7545207Z</t>
-  </si>
-  <si>
-    <t>Er2oCUuoCkKX8CAjW5UE4GQAKaCr</t>
-  </si>
-  <si>
-    <t>Add New Audience to target (Hidden audience - Office managers, team mgrs)</t>
-  </si>
-  <si>
     <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-12T03:09:28.9045295Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
   </si>
   <si>
@@ -449,7 +455,7 @@
     <t>ADS- Setup, * Project</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:02.1022309Z</t>
+    <t>2026-10-14T12:29:40.3893022Z</t>
   </si>
   <si>
     <t>AKJYMO8S3Ea60DEEzc28LmQAOj-s</t>
@@ -473,7 +479,7 @@
     <t>LinkedIn</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:04.3013042Z</t>
+    <t>2026-10-14T12:29:42.7023666Z</t>
   </si>
   <si>
     <t>mMmFoceMMEmFO3y4JA0afGQAEw2l</t>
@@ -488,7 +494,7 @@
     <t>8584098409380764043P.</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:09.3006093Z</t>
+    <t>2026-10-14T12:29:44.8960597Z</t>
   </si>
   <si>
     <t>br8t-rntrUOjV55q25GzK2QAA9p-</t>
@@ -512,7 +518,7 @@
     <t>Event</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:12.1402643Z</t>
+    <t>2026-10-14T12:29:47.4443681Z</t>
   </si>
   <si>
     <t>vhFU2Oj87EGqLsTanL_ShWQAHjKR</t>
@@ -530,7 +536,7 @@
     <t>8584100629724288304P"</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:14.9114159Z</t>
+    <t>2026-10-14T12:29:49.6521131Z</t>
   </si>
   <si>
     <t>X_0Uh7TKuEW8MfqWzw4nM2QACOGm</t>
@@ -551,7 +557,7 @@
     <t>8584100630366877635P(</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:18.6139339Z</t>
+    <t>2026-10-14T12:29:52.3069550Z</t>
   </si>
   <si>
     <t>HgndDzXESEuaNElMclYyzmQAEoEe</t>
@@ -575,7 +581,7 @@
     <t>Facebook</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:21.6603132Z</t>
+    <t>2026-10-14T12:29:55.6621255Z</t>
   </si>
   <si>
     <t>LfB9M_IOAE2qbOfWv5iEDmQAL2v1</t>
@@ -607,7 +613,7 @@
     <t>Web-dotcom</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:24.1052596Z</t>
+    <t>2026-10-14T12:29:57.7218275Z</t>
   </si>
   <si>
     <t>leF1KFTmkUuLXCazqQQJTmQAE25d</t>
@@ -631,7 +637,7 @@
     <t>8584100722915455148P&amp;</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:26.5970111Z</t>
+    <t>2026-10-14T12:30:00.1620738Z</t>
   </si>
   <si>
     <t>adeUyIiUaUeiJYqmNDs2IGQANrAt</t>
@@ -655,7 +661,7 @@
     <t>Open AI</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:30.3533423Z</t>
+    <t>2026-10-14T12:30:03.2200942Z</t>
   </si>
   <si>
     <t>4chpN0fZ2UKOHZEibPWeN2QAPcZQ</t>
@@ -679,7 +685,7 @@
     <t>8584100801791421405PM</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:33.3921504Z</t>
+    <t>2026-10-14T12:30:08.7218745Z</t>
   </si>
   <si>
     <t>K9hqCEij20CrlLBOi8jLaGQAEfzk</t>
@@ -712,7 +718,7 @@
     <t>Event, * Project</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:35.6847047Z</t>
+    <t>2026-10-14T12:30:11.9463257Z</t>
   </si>
   <si>
     <t>TMCfdcZXiUWBvUiiI_Rrd2QAMnum</t>
@@ -721,12 +727,6 @@
     <t>steelcase.kr — align with Korean team on website plan</t>
   </si>
   <si>
-    <t>hXWXxcacR0e8OSPDfuHME2QAMCsP</t>
-  </si>
-  <si>
-    <t>Next Week</t>
-  </si>
-  <si>
     <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-09T04:36:18.6669503Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
   </si>
   <si>
@@ -748,7 +748,7 @@
     <t>Web-dotcom, * Project</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:39.4299634Z</t>
+    <t>2026-10-14T12:30:15.9077867Z</t>
   </si>
   <si>
     <t>5OXEHuDDIEW6grPiG9vrXGQAP5Hk</t>
@@ -772,7 +772,7 @@
     <t>8584100864388426655PB</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:41.9172871Z</t>
+    <t>2026-10-14T12:30:18.9278201Z</t>
   </si>
   <si>
     <t>DaeTMcz8QUmTxhgk52nnimQALPOs</t>
@@ -796,7 +796,7 @@
     <t>8584100864919263006PE</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:44.7278586Z</t>
+    <t>2026-10-14T12:30:21.7429372Z</t>
   </si>
   <si>
     <t>2Rn56KJET0mNFn3o5rQTNmQAPyyS</t>
@@ -826,7 +826,7 @@
     <t>Hubspot, * Project</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:47.0363183Z</t>
+    <t>2026-10-14T12:30:24.4544058Z</t>
   </si>
   <si>
     <t>Md1xDFpLy0WPMKnOvCrDKGQAN204</t>
@@ -850,7 +850,7 @@
     <t>8584100866138677186PJ</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:49.9107043Z</t>
+    <t>2026-10-14T12:30:27.3311782Z</t>
   </si>
   <si>
     <t>VSxpiViweEKP0dqcIz8ulWQAP2dl</t>
@@ -874,7 +874,7 @@
     <t>8584100866821877089P5</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:53.3328954Z</t>
+    <t>2026-10-14T12:30:30.7897056Z</t>
   </si>
   <si>
     <t>SIJSXbO4_E-e-wdloHFW3mQAJHq0</t>
@@ -892,7 +892,7 @@
     <t>8584100924319716018PK</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:56.1687349Z</t>
+    <t>2026-10-14T12:30:36.3963351Z</t>
   </si>
   <si>
     <t>Ct0P1Ky-s0CCCiHy_ka_wWQAOcJC</t>
@@ -910,7 +910,7 @@
     <t>8584100925786138949P9</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:59.8869224Z</t>
+    <t>2026-10-14T12:30:38.8153340Z</t>
   </si>
   <si>
     <t>3JUkRDhCJkucx0XFzr5sjWQAH-dF</t>
@@ -934,7 +934,7 @@
     <t>ADS- Setup</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:03.0201191Z</t>
+    <t>2026-10-14T12:30:41.1890876Z</t>
   </si>
   <si>
     <t>pLnoVyTy-UKfHxF2NSHky2QAFwrH</t>
@@ -952,7 +952,7 @@
     <t>8584100926437255670P@</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:06.1789878Z</t>
+    <t>2026-10-14T12:30:43.8836894Z</t>
   </si>
   <si>
     <t>MOFArwZE7kKgU49WeKVKnmQALrej</t>
@@ -976,7 +976,7 @@
     <t>Hubspot</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:08.7104515Z</t>
+    <t>2026-10-14T12:30:46.8683089Z</t>
   </si>
   <si>
     <t>ClotRw8fYkmqkPmLV8QW8WQAOm2j</t>
@@ -994,7 +994,7 @@
     <t>8584100928881490685P8</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:11.1198838Z</t>
+    <t>2026-10-14T12:30:49.2760627Z</t>
   </si>
   <si>
     <t>EaEojZnfCkaUxX7WPDt-dWQAF876</t>
@@ -1012,7 +1012,7 @@
     <t>8584100929022780743P1</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:13.6218929Z</t>
+    <t>2026-10-14T12:30:51.7547498Z</t>
   </si>
   <si>
     <t>o7V32ZN38UqAt4wcI0W5lWQACoFI</t>
@@ -1030,7 +1030,7 @@
     <t>8584100929198708177P7</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:16.8881603Z</t>
+    <t>2026-10-14T12:30:57.9800242Z</t>
   </si>
   <si>
     <t>SIs9dBetBES9kMdCGI7N9GQAMOFv</t>
@@ -1048,7 +1048,7 @@
     <t>8584100929317369770P$</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:19.8688268Z</t>
+    <t>2026-10-14T12:31:01.7499572Z</t>
   </si>
   <si>
     <t>-c3HJoSuAkCRbyM7OJBEgGQAEXGe</t>
@@ -1078,7 +1078,7 @@
     <t>SEO, * Project</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:22.8575776Z</t>
+    <t>2026-10-14T12:31:04.8224547Z</t>
   </si>
   <si>
     <t>n_Q762Pp0kqZTEEvn66eDWQACiVW</t>
@@ -1111,7 +1111,7 @@
     <t>Ai</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:25.7233049Z</t>
+    <t>2026-10-14T12:31:07.5213322Z</t>
   </si>
   <si>
     <t>Bzl3nPAinEeLZJ2r_afpEmQACBVw</t>
@@ -1135,7 +1135,7 @@
     <t>SM-Post</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:28.1350253Z</t>
+    <t>2026-10-14T12:31:10.3774956Z</t>
   </si>
   <si>
     <t>qhPT9Xxq-0mecuLvgcP80GQAFPOa</t>
@@ -1159,7 +1159,7 @@
     <t>ADS- Planning, Open AI</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:30.4473847Z</t>
+    <t>2026-10-14T12:31:12.9870846Z</t>
   </si>
   <si>
     <t>b4aSSkfslUWIXEmfIwKaJGQADExe</t>
@@ -1183,7 +1183,7 @@
     <t>Web-dotcom, ADS- Planning</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:32.8117361Z</t>
+    <t>2026-10-14T12:31:15.5246887Z</t>
   </si>
   <si>
     <t>vrDE2BWIMUSU_s6QsxQKrGQAHPPp</t>
@@ -1201,7 +1201,7 @@
     <t>8584101811517615722PL</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:35.3493244Z</t>
+    <t>2026-10-14T12:31:17.7197300Z</t>
   </si>
   <si>
     <t>sRwBGXos00e2k4zBigGIAWQAPUmg</t>
@@ -1231,7 +1231,677 @@
     <t>Email-APAC News</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:38.1160396Z</t>
+    <t>2026-10-14T12:31:20.3693323Z</t>
+  </si>
+  <si>
+    <t>panY5gjBbEm7WcJFrDSTuWQAIjze</t>
+  </si>
+  <si>
+    <t>Look into audience for LinkedIn based on the GCC file shared</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-07T02:54:01.5391153Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-07T02:54:01.5391739Z</t>
+  </si>
+  <si>
+    <t>8584102653039805165PN</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:23.1447505Z</t>
+  </si>
+  <si>
+    <t>lwfxeYVKRkyr1PoDBym412QAKf8F</t>
+  </si>
+  <si>
+    <t>Women of Steel Playlist - Unlisted</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-07T02:13:44.7391879Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-07T02:13:44.7392456Z</t>
+  </si>
+  <si>
+    <t>8584102677207842506P:</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:25.6238176Z</t>
+  </si>
+  <si>
+    <t>ZboAyoQAMU2jV6BcqPG12WQAMr-U</t>
+  </si>
+  <si>
+    <t>WorkTech Singapore Social post</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-06T03:11:43.9499892Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-06T03:11:43.950044Z</t>
+  </si>
+  <si>
+    <t>[{"resourceLink":"https://steelcase.sharepoint.com/sites/BrandcomDigitalTeamTaskRequest/Shared%20Documents/ss.jpg","value":{"@odata.type":"#microsoft.graph.plannerExternalReference","alias":"ss.jpg","type":"Other","previewPriority":"8584103504ZJ","lastModifiedDateTime":"2026-10-06T03:13:45.786095Z","lastModifiedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"}}}}]</t>
+  </si>
+  <si>
+    <t>8584103506416161534PI</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:28.2680742Z</t>
+  </si>
+  <si>
+    <t>eidBTD4wx0ef5Ew2aIMe1WQAITot</t>
+  </si>
+  <si>
+    <t>Add a banner - all WL pages</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-05T07:18:00.7791066Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-05T07:18:00.7791739Z</t>
+  </si>
+  <si>
+    <t>2026-10-16T10:00:00Z</t>
+  </si>
+  <si>
+    <t>[{"resourceLink":"https://steelcase.sharepoint.com/sites/BrandcomDigitalTeamTaskRequest/Shared%20Documents/1.png","value":{"@odata.type":"#microsoft.graph.plannerExternalReference","alias":"1.png","type":"Other","previewPriority":"8584104221576503676P@","lastModifiedDateTime":"2026-10-05T07:19:47.8621433Z","lastModifiedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"}}}}]</t>
+  </si>
+  <si>
+    <t>8584104222649895193P.</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:30.8647391Z</t>
+  </si>
+  <si>
+    <t>ta48yj6nekClG4KtBy5UUWQAIwoT</t>
+  </si>
+  <si>
+    <t>Planning Ideas - Widen</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-01T12:00:39.8045085Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-10-01T12:00:39.8045617Z</t>
+  </si>
+  <si>
+    <t>{"category3":true}</t>
+  </si>
+  <si>
+    <t>8584107509057119924PK</t>
+  </si>
+  <si>
+    <t>Web-Widen</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:33.8711401Z</t>
+  </si>
+  <si>
+    <t>0zCmt3_wEUeajg_HWjEu9mQAFNZP</t>
+  </si>
+  <si>
+    <t>To check Hubspot segmentation on users - Digital call</t>
+  </si>
+  <si>
+    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T07:22:47.3278722Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-30T07:22:47.3279201Z</t>
+  </si>
+  <si>
+    <t>8584108539781878050P&lt;</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:36.7780481Z</t>
+  </si>
+  <si>
+    <t>0Di9eFqpfkG1GDPeIxzdl2QABbGp</t>
+  </si>
+  <si>
+    <t>Creating webpages for Work Better 7 articles</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:30:44.9858742Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-30T03:30:44.9859208Z</t>
+  </si>
+  <si>
+    <t>[https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Work%20Better/WB%20Spring%202026%20(WB7%20A%20New%20Mindset)/Translation?csf=1&amp;web=1&amp;e=668MHy](https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Work%20Better/WB%20Spring%202026%20%28WB7%20A%20New%20Mindset%29/Translation?csf=1&amp;amp;web=1&amp;amp;e=668MHy)</t>
+  </si>
+  <si>
+    <t>[{"resourceLink":"https://steelcase.sharepoint.com/sites/BrandcomDigitalTeamTaskRequest/_layouts/15/Doc.aspx?sourcedoc=%7B8E757982-BEA4-4F7C-9545-E4C67FDB4FE5%7D&amp;file=Work%20Better%207%20-%20Articles%20Extraction.xlsx&amp;action=default&amp;mobileredirect=true","value":{"@odata.type":"#microsoft.graph.plannerExternalReference","alias":"Work Better 7 - Articles Extraction.xlsx","type":"Excel","previewPriority":"8584108678569325348P+","lastModifiedDateTime":"2026-09-30T03:31:28.5715201Z","lastModifiedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"}}}}]</t>
+  </si>
+  <si>
+    <t>8584108679005296951P9</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:39.0887248Z</t>
+  </si>
+  <si>
+    <t>Af4lfuRuSkqJ9O-gfRgBHWQAPEPT</t>
+  </si>
+  <si>
+    <t>Migration SE Collection webpage in Japanese</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:28:55.2129923Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-30T03:28:45.9902867Z</t>
+  </si>
+  <si>
+    <t>2026-10-09T10:00:00Z</t>
+  </si>
+  <si>
+    <t>[https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/JP?d=wc1b139dccfe744978f7591ea11a8b649&amp;csf=1&amp;web=1&amp;e=S9A9B7](https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/JP?d=wc1b139dccfe744978f7591ea11a8b649&amp;amp;csf=1&amp;amp;web=1&amp;amp;e=S9A9B7)</t>
+  </si>
+  <si>
+    <t>8584108680195387782PH</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:41.6136001Z</t>
+  </si>
+  <si>
+    <t>GLcy1eg2bE696YRhutkA32QANKbi</t>
+  </si>
+  <si>
+    <t>Migration SE Collection webpage in Chinese</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:27:43.4234896Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-30T03:27:37.3381237Z</t>
+  </si>
+  <si>
+    <t>[https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/CN?d=wf206f8f1d6aa4affb5c004c9a08f5ba1&amp;csf=1&amp;web=1&amp;e=Jflwbg](https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/CN?d=wf206f8f1d6aa4affb5c004c9a08f5ba1&amp;amp;csf=1&amp;amp;web=1&amp;amp;e=Jflwbg)</t>
+  </si>
+  <si>
+    <t>8584108680882325673PM</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:44.4077150Z</t>
+  </si>
+  <si>
+    <t>IvDVqKsoXkCEQ48JG8edCWQAMSvo</t>
+  </si>
+  <si>
+    <t>HPS external page</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:22:20.8909643Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-30T03:22:20.8910212Z</t>
+  </si>
+  <si>
+    <t>https://www.steelcase.com/high-performance-seating/</t>
+  </si>
+  <si>
+    <t>8584108684047522812P5</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:46.6758130Z</t>
+  </si>
+  <si>
+    <t>ovv8TGpKtEifKB57xgF6tGQAOkJf</t>
+  </si>
+  <si>
+    <t>Hubspot Segmentation - Japan</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-29T08:37:21.8794304Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-29T08:37:17.0657289Z</t>
+  </si>
+  <si>
+    <t>2026-09-29T10:00:00Z</t>
+  </si>
+  <si>
+    <t>8584109359084977527P2</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:49.9917731Z</t>
+  </si>
+  <si>
+    <t>XdMTSMZ3-0qaTii7SWE_CmQAIdG2</t>
+  </si>
+  <si>
+    <t>ABM Targeting</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:03:01.246682Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-29T06:44:56.7843072Z</t>
+  </si>
+  <si>
+    <t>{"category21":true,"category23":true}</t>
+  </si>
+  <si>
+    <t>NOTE: Building the ABM target list from the 35 APAC priority accounts (shared with Chia May Yee 10/2) layered with Michelle's GCC/SAM list. Files: FY26 Top 35 - GCC.xlsx (SharePoint: OrderLeadTimeAgility &gt; OLTA) and FY26 Master GCC Client List.xlsx (SRNProposalTeam &gt; General). Feeds Gus Wick's tracking one-pager and the LinkedIn Top Companies audience.</t>
+  </si>
+  <si>
+    <t>[{"id":"26d736c3fd5b4b2d9ff8d0b87444e1d1","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Lock the final ABM target list for the media plan","orderHint":"858410087166","lastModifiedDateTime":"2026-10-09T04:22:22.7507964Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"fc50afae2c824e6d890fc8e7bdb7a6fc","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Define tiering criteria (Tier 1/2/3) for targeting intensity","orderHint":"8584100871GJ","lastModifiedDateTime":"2026-10-12T00:52:30.1246544Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"f6b479830461401d9ec2aef14e725c06","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Pull the 35 APAC priority accounts with Chia May Yee","orderHint":"8584100872278331186P-","lastModifiedDateTime":"2026-10-09T04:33:22.1901748Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"064e00fc42e54ba2a8e38840ac058a79","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Layer in the GCC and SAM account list from Michelle","orderHint":"8584100871Z/","lastModifiedDateTime":"2026-10-12T00:52:28.9455031Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"702775ff6aa94eb2b8ad7bb4704aaa2e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Align the account list with Sales (Japan/Korea/India leads)","orderHint":"85841008719I","lastModifiedDateTime":"2026-10-09T04:22:18.5960081Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"0b1e51d75519425e9e7af2fc529344b5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Map accounts to the LinkedIn Top Companies audience","orderHint":"8584100871&gt;L","lastModifiedDateTime":"2026-10-09T04:33:55.2686462Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584109426487303270PN</t>
+  </si>
+  <si>
+    <t>Leadgen, * Project</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:53.6308523Z</t>
+  </si>
+  <si>
+    <t>NPv-ewMX5UOw_bUAhllGJmQAM7n8</t>
+  </si>
+  <si>
+    <t>Gated LPs for consultation, downloads + tracking</t>
+  </si>
+  <si>
+    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-29T06:42:39.1644677Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-29T06:42:39.1645232Z</t>
+  </si>
+  <si>
+    <t>2026-10-13T10:00:00Z</t>
+  </si>
+  <si>
+    <t>{"category5":true}</t>
+  </si>
+  <si>
+    <t>Hi Adam, as discussed on Teams, we need a gated landing page for enquiries. This ties in with the offer of "Personalize customization" that we want our audience to eventually fill up. This is specifically for non-lead gen paid campaigns where we need a page to direct audiences to (i.e. eDMs - email nurture series, organic posts). It will also be used in the final email in our email nurture series._x000D_
+Corrine has shared that there was an existing one in the past brand campaign that we can look to use/update: https://www.steelcase.com/asia-en/work-better-campaign/ but if you feel we just need a simpler LP instead of having all these information, feel free to suggest.</t>
+  </si>
+  <si>
+    <t>8584109427863526779P?</t>
+  </si>
+  <si>
+    <t>Email-EDM</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:31:57.2681595Z</t>
+  </si>
+  <si>
+    <t>6Y4ER53BpU6JV-XbW9HTfmQAPQqq</t>
+  </si>
+  <si>
+    <t>Creative Agency</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:03:08.740805Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-29T06:39:51.7671244Z</t>
+  </si>
+  <si>
+    <t>NOTE: Scoping whether the team needs an external creative agency (campaigns, assets, markets) vs the current WSF setup. Needs Michelle's sign-off on the recommendation.</t>
+  </si>
+  <si>
+    <t>[{"id":"b4d49e3614e1441b9a529d487d3c614e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Shortlist agencies, brief them, collect proposals","orderHint":"85841008713M","lastModifiedDateTime":"2026-10-09T04:22:45.0883122Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"a6b58bda89ac4f6fa058d43d9f7f954e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Evaluate on B2B portfolio, APAC chops, and pricing","orderHint":"858410087127","lastModifiedDateTime":"2026-10-09T04:22:48.9378323Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"39747a22abf84fed9cceb4d2414d7e71","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Recommend and get Michelle's sign-off","orderHint":"85841008711X:","lastModifiedDateTime":"2026-10-09T04:22:52.6383343Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"d9a5a1a68f074f3b940535401072fd37","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Assess the incumbent setup (WSF team) vs external need","orderHint":"858410087152","lastModifiedDateTime":"2026-10-09T04:22:41.0090508Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"bdeeed9b5c3c4813a629de538f2d9336","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410086E","lastModifiedDateTime":"2026-10-09T04:50:43.0304639Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"0343a657e8ae43fca15736bffdcb8608","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define the creative scope — campaigns, assets, markets needed","orderHint":"8584100871895639791P%","lastModifiedDateTime":"2026-10-09T04:22:35.9390415Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584109429537690343P=</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:00.4297545Z</t>
+  </si>
+  <si>
+    <t>furFAgXsvUi5w6PD27OGsGQAFBnP</t>
+  </si>
+  <si>
+    <t>launch new page after form filled in HS</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:04.1091837Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-28T04:11:53.5702771Z</t>
+  </si>
+  <si>
+    <t>Decision: Thank you page is the best_x000D_
+_x000D_
+NOTE: Post-submit experience for HubSpot lead forms — thank-you page vs redirect, with tracking pixels. Critical: test that the Salesforce sync still fires correctly after the redirect is wired.</t>
+  </si>
+  <si>
+    <t>[{"id":"be9a6df72aee420badf777e15057193a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Define the post-submit experience — thank-you page vs redirect","orderHint":"8584100871622563634PB","lastModifiedDateTime":"2026-10-09T04:34:28.5928074Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b26f851fce024b8ea6624295aa69f0e5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft the page copy and CTA","orderHint":"8584100870\\,","lastModifiedDateTime":"2026-10-09T04:23:07.0285872Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"caaa31b72d09433a822b8aecbedd0289","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the page in HubSpot with tracking pixels","orderHint":"8584100870J+","lastModifiedDateTime":"2026-10-09T04:23:11.3012813Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"de0b5014ec9b48d9adc1aef20b5def5d","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Test the full flow — submit, redirect, Salesforce sync intact","orderHint":"8584100870&lt;B","lastModifiedDateTime":"2026-10-09T04:23:24.499444Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"10f8c592845d4b9494efaaf4ee037ec9","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Launch and monitor conversion","orderHint":"85841008709=","lastModifiedDateTime":"2026-10-09T04:23:28.843656Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"a791009c5dac4d1b9185a92b56b19775","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Wire the form to redirect on submit","orderHint":"8584100870A*","lastModifiedDateTime":"2026-10-09T04:23:15.8251031Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584110382319429739PH</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:03.0035708Z</t>
+  </si>
+  <si>
+    <t>iwKT-GjT6kOaJ3JJFD9_z2QAMoie</t>
+  </si>
+  <si>
+    <t>Contentful Project</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:48.730709Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-21T08:13:13.8808502Z</t>
+  </si>
+  <si>
+    <t>NOTE: CMS migration/streamlining work. Check the vault BrandCom notes for current status.</t>
+  </si>
+  <si>
+    <t>[{"id":"231eef543e5541c8b0159d689827db68","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Make deck","orderHint":"8584114691865796372P#","lastModifiedDateTime":"2026-09-23T04:29:18.9150332Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"54a4732733b04da59a9af7409b8b374a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410CF","lastModifiedDateTime":"2026-10-09T04:56:29.426033Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c53910754d59454ab237f8fc1f0db236","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410W.","lastModifiedDateTime":"2026-10-09T04:56:20.5310665Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584116285516486084PE</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:06.7303633Z</t>
+  </si>
+  <si>
+    <t>eWzMNDoXhkqBQpzanbpjzGQAJj7Q</t>
+  </si>
+  <si>
+    <t>Combining Tanya + Lead-Max</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:16.5855687Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-21T06:36:56.7047928Z</t>
+  </si>
+  <si>
+    <t>{"category22":true,"category23":true}</t>
+  </si>
+  <si>
+    <t>Scope out project_x000D_
+_x000D_
+NOTE: Tanya owns Village/digital experience touchpoints; Lead-Max is the B2B lead enrichment flow. Map both and draft a combined scope with owners.</t>
+  </si>
+  <si>
+    <t>[{"id":"74a4b9fc2bdf41268f22a438da9b0b43","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Identify the integration points between the two","orderHint":"8584100870F'","lastModifiedDateTime":"2026-10-09T04:24:04.9098563Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"514abfab9c2e472b8b5a0d005d91d978","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Estimate effort and timeline","orderHint":"858410087073","lastModifiedDateTime":"2026-10-09T04:24:13.6798371Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b4696bf623c34cac87ad5cc6b5e14171","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft the combined scope — objectives, deliverables, owners","orderHint":"8584100870&lt;(","lastModifiedDateTime":"2026-10-09T04:24:08.8920602Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"9dd22e528a4e4a109f10889af81c0bdd","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Map what Tanya owns today (Village, digital experience touchpoints)","orderHint":"8584100871104664726P9","lastModifiedDateTime":"2026-10-09T04:23:55.0320611Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2662bcf3e086434c835b325a62eb6388","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Align with Tanya and get sign-off to proceed","orderHint":"85841008704N","lastModifiedDateTime":"2026-10-09T04:24:18.2767167Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b778f641303e4e6f96d6498a33875faa","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410086/","lastModifiedDateTime":"2026-10-09T04:52:41.0817159Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"58bd9ef32c154bc89f6ac58540da2cca","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Map the Lead-Max flow — enrichment, routing, handover","orderHint":"8584100870Y&gt;","lastModifiedDateTime":"2026-10-09T04:23:58.9520399Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"130a04600f7a4b56b09c7538f3fc7d62","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085Y+","lastModifiedDateTime":"2026-10-09T04:52:49.1404711Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584116343288131154PI</t>
+  </si>
+  <si>
+    <t>Ai, * Project</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:09.1017993Z</t>
+  </si>
+  <si>
+    <t>3atuqLPaoUu7LuKHp43rw2QAIeHI</t>
+  </si>
+  <si>
+    <t>exploring checkin solution for Dani's event.</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:10:09.2109177Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:13:30.1552183Z</t>
+  </si>
+  <si>
+    <t>NOTE: Danni = Danielle Gu. Need a check-in solution (QR / badge printing / walk-ins) for her event — confirm date, venue, headcount with her first.</t>
+  </si>
+  <si>
+    <t>[{"id":"6671ec0e86ec446aa8b9f2dee0bbb4c9","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Shortlist check-in tools and compare","orderHint":"85841008702G","lastModifiedDateTime":"2026-10-09T04:24:36.8418153Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"8e6048f454e949c393be7e472ffeb34a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085EL","lastModifiedDateTime":"2026-10-09T04:53:18.8986374Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c92e1085bf6548a4819d40b7a97a0d3f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Recommend and set up for the event","orderHint":"858410086\\3","lastModifiedDateTime":"2026-10-09T04:24:45.6720052Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"bd3a40a0eefd4db0898f1fd2ee5dbf7d","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm event details with Dani — date, venue, expected headcount","orderHint":"8584100870765289684PG","lastModifiedDateTime":"2026-10-09T04:24:28.9776818Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"4ca61e2f12584b7b98fde744f8ac5d10","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define check-in requirements (QR, badge printing, walk-ins)","orderHint":"85841008704+","lastModifiedDateTime":"2026-10-09T04:24:32.7162704Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"3a8c9267752c4f0fa9135560a0225275","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Test the top option end-to-end","orderHint":"858410087015","lastModifiedDateTime":"2026-10-09T04:24:41.0493597Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121541353582513P8</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:11.5263888Z</t>
+  </si>
+  <si>
+    <t>69DUvv6DpEGI7MvjBPJIVGQAJkXF</t>
+  </si>
+  <si>
+    <t>Sorting out tracking issues Tim Merkel discussion with Katy.</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:10:42.0391989Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:09:01.8563835Z</t>
+  </si>
+  <si>
+    <t>2026-08-18T10:00:00Z</t>
+  </si>
+  <si>
+    <t>{"category13":true,"category23":true}</t>
+  </si>
+  <si>
+    <t>NOTE: Open tracking gaps (UTMs, pixels, CRM sync). Sync with Katy on the paid side first, then bring the issue list to Tim Merkel with agreed owners and fixes.</t>
+  </si>
+  <si>
+    <t>[{"id":"56856271152f468893deffd07fcde6d5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Hold the discussion and agree owners + fixes","orderHint":"858410086AM","lastModifiedDateTime":"2026-10-09T04:25:15.3755464Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2cef2967e1d5485ebf5522357f1901be","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm reporting is accurate post-fix","orderHint":"858410086;&lt;","lastModifiedDateTime":"2026-10-09T04:25:24.3717245Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ddf5dfd8510e4e9888cca4e337fe07b4","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"List the known tracking issues (UTMs, pixels, CRM sync gaps)","orderHint":"8584100870417444230P$","lastModifiedDateTime":"2026-10-09T04:25:03.7692376Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"18a9d438c6054a79831d9729ced02e24","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Sync with Katy on what's broken on the paid side","orderHint":"858410086\\4","lastModifiedDateTime":"2026-10-09T04:25:07.5179187Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"db92e53e84f048a882b5d80ef33f7330","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Prep the issue list and questions for Tim Merkel","orderHint":"858410086J$","lastModifiedDateTime":"2026-10-09T04:25:11.5096083Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"cadf547371e94b80947f2bc9b01cdf9b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085XO","lastModifiedDateTime":"2026-10-09T04:53:34.7331328Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"8109fee5c5e4401187951ed599f17219","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Implement fixes and verify data flows","orderHint":"858410086=E","lastModifiedDateTime":"2026-10-09T04:25:20.0627738Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c134e7cba5134c8a92e1f6c714272201","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085E\"","lastModifiedDateTime":"2026-10-09T04:53:42.9821417Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121544036796805P&lt;</t>
+  </si>
+  <si>
+    <t>Report, * Project</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:15.1140939Z</t>
+  </si>
+  <si>
+    <t>cnIAqFLCJUGxQosU2Xf8YWQADDv9</t>
+  </si>
+  <si>
+    <t>Create SOP for all processes</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T12:56:39.5506397Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:08:43.4238999Z</t>
+  </si>
+  <si>
+    <t>{"category23":true}</t>
+  </si>
+  <si>
+    <t>NOTE: SOPs for recurring team processes — campaigns, reporting, lead handling, events. Review with Rebecca and Aisah; publish in the shared team folder.</t>
+  </si>
+  <si>
+    <t>[{"id":"aeb87cdbfd25479dbdbbe1fbe166c4e0","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Prioritize by frequency and pain","orderHint":"858410086\\F","lastModifiedDateTime":"2026-10-09T04:35:07.7205755Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2d1a30094481493e94389f4054f1a96e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Review with Rebecca and Aisah","orderHint":"858410086AJ","lastModifiedDateTime":"2026-10-09T04:25:47.3927311Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ee0597e158d14e169eb8195a5c408d72","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft each SOP — steps, owners, tools, templates","orderHint":"858410086JI","lastModifiedDateTime":"2026-10-09T04:25:43.2229748Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7b2d8aae7cdd4ba68425337457cb97f3","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Publish in the shared team folder","orderHint":"858410086=(","lastModifiedDateTime":"2026-10-09T04:25:51.6047727Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"03d22c86c6c543608fc98e4ade5ba651","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Set a quarterly review reminder","orderHint":"858410086;K","lastModifiedDateTime":"2026-10-09T04:25:55.8490471Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7ed5c1db3e53422fa82d5f87e1272035","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Inventory all recurring team processes (campaigns, reporting, lead handling, events)","orderHint":"8584100870100467838P;","lastModifiedDateTime":"2026-10-09T04:25:35.4653589Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121544220929001P5</t>
+  </si>
+  <si>
+    <t>* Project</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:17.3846898Z</t>
+  </si>
+  <si>
+    <t>FRfiIINxl02XF9Di7TUxX2QAPoad</t>
+  </si>
+  <si>
+    <t>AI SDR - Talk to Lim</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:07.4920341Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:08:20.0706731Z</t>
+  </si>
+  <si>
+    <t>NOTE: Lim = Wen Yi Lim (filed the 'Update Lead Times' request 10/5). Align on AI SDR pilot status and next-phase needs. Related vault folder: Ai-SDR/.</t>
+  </si>
+  <si>
+    <t>[{"id":"08b100c3e0a94f1bb7692a9843b71ce0","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085XD","lastModifiedDateTime":"2026-10-09T04:54:00.0335375Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"8f965aa201bc4ad589e654c6e2fcc526","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Action the follow-ups","orderHint":"85841008690X0","lastModifiedDateTime":"2026-10-09T04:26:23.3508937Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"63864ea3dd0947ea88ce78f3266d8b80","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Align on what you need from Lim for the next phase","orderHint":"85841008694M","lastModifiedDateTime":"2026-10-09T04:26:10.7658217Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"932b52c521444ae9a64bd5f6b7dfc11f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Update the Ai-SDR project note with outcomes","orderHint":"85841008691N","lastModifiedDateTime":"2026-10-09T04:26:19.0190685Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"37e2f237e157483d8497601b3a798788","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Prep the AI SDR status — pilot results, call volumes, bookings","orderHint":"8584100869788535167P.","lastModifiedDateTime":"2026-10-09T04:26:06.654577Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"f02d471614fb4c30b291625fe83a26fa","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Hold the discussion and capture decisions","orderHint":"85841008692M","lastModifiedDateTime":"2026-10-09T04:26:14.7999907Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121544454497814P/</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:19.7484639Z</t>
+  </si>
+  <si>
+    <t>IRN2kdT_j0K6rGD7b0_ZuGQAJdXG</t>
+  </si>
+  <si>
+    <t>Replace Clickup with Microsoft Planner</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:44.453109Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:07:48.5565783Z</t>
+  </si>
+  <si>
+    <t>NOTE: Migrating the team's work from ClickUp to Planner (71 tasks in this plan). Task inventory: https://steelcase-my.sharepoint.com/:x:/p/alau2/IQAR4MiHA6b0RK6HK6WoJFngASyjOPeCgRCCeYwcAmUdQnw?e=CBDcl5 — then brief the 8 Brand Comm APAC leaders and archive ClickUp.</t>
+  </si>
+  <si>
+    <t>[{"id":"05106b2ebd064c5badb47aca507ba5a3","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Brief the 8 Brand Comm APAC leaders on the Planner workflow","orderHint":"85841008750ZC","lastModifiedDateTime":"2026-10-09T04:16:19.1515242Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"4e43c9ee7af44a2b8d4ca845cdffd3d2","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Run team training once Michelle green-lights","orderHint":"85841006X6","lastModifiedDateTime":"2026-10-09T11:08:36.3430913Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"9dc535da611945a3a3907b5ac7b7ab9f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"PlannerHub dashboard (go.steelcase.com) shared with Michelle","orderHint":"85841007C","lastModifiedDateTime":"2026-10-09T11:08:31.8750677Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"18ea202c46964c98aa2f1dd8b51d86b7","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Design Planner plan/bucket/label structure to mirror ClickUp","orderHint":"85841008755/","lastModifiedDateTime":"2026-10-09T04:54:19.161359Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"073adbe55c4f40069c32db2b1d9dcba4","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Audit ClickUp - list spaces, lists and open tasks to migrate","orderHint":"8584100875863035531P;","lastModifiedDateTime":"2026-10-09T04:15:59.2088453Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7e39957c813e4b809460af5611f85139","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Recreate buckets and labels in Planner, migrate open tasks","orderHint":"85841008752O","lastModifiedDateTime":"2026-10-09T04:16:11.17932Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"fcaab957a4e7406dbfa0e5945f5646cc","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Re-link key attachments and SharePoint references","orderHint":"85841008751W&amp;","lastModifiedDateTime":"2026-10-09T04:16:15.1992954Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1e224496b9a14de6bf779930567277d8","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm Michelle's monthly/quarterly reporting view, then archive ClickUp","orderHint":"85841008750F1","lastModifiedDateTime":"2026-10-09T04:16:23.1370245Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"3b976c4ed8a545d29b5001bc5f7e99cf","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Export task inventory from ClickUp (assignees, due dates, descriptions)","orderHint":"85841008753K","lastModifiedDateTime":"2026-10-09T04:16:07.5559931Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121544769896651P.</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:21.9889101Z</t>
+  </si>
+  <si>
+    <t>G4J5kNOAxUO_fKW-hi3A-WQABaSH</t>
+  </si>
+  <si>
+    <t>Dashboard: Email reporting</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:23.9117786Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:07:24.7838288Z</t>
+  </si>
+  <si>
+    <t>NOTE: Email performance dashboard from HubSpot data — sends, opens, CTR, leads, MQLs by campaign and market, with MoM trends. Validate against HubSpot native reports.</t>
+  </si>
+  <si>
+    <t>[{"id":"531a64cdae07479a9c60ee02c76e19ae","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define the email KPIs — sends, opens, CTR, leads, MQLs","orderHint":"8584100869293009532PF","lastModifiedDateTime":"2026-10-09T04:26:56.2093928Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"486a17ca4ae14631928e0dd59bd02f44","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Validate numbers against HubSpot's native reports","orderHint":"85841008689O","lastModifiedDateTime":"2026-10-09T04:27:13.4220894Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"920b4ab22f804847aa2eedcd17f8965a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the email performance view by campaign and market","orderHint":"8584100868H6","lastModifiedDateTime":"2026-10-09T04:27:04.5498117Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7ef8279aefd74778ab01a579fcdd4072","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085X3","lastModifiedDateTime":"2026-10-09T04:54:35.5231109Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"aabacd9c521c4589881ba3ace8841f58","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Share with the team and set the refresh cadence","orderHint":"85841008686)","lastModifiedDateTime":"2026-10-09T04:27:22.1613544Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"fb19c7df00b9437eb9346513aa184489","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Add month-on-month trend charts","orderHint":"8584100868&gt;G","lastModifiedDateTime":"2026-10-09T04:27:08.4046179Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ea92e393a940403ab6a05fd32fd276cb","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Connect HubSpot email data to the dashboard source","orderHint":"8584100868Z9","lastModifiedDateTime":"2026-10-09T04:27:00.1394205Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121545007319813PC</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:24.6656305Z</t>
+  </si>
+  <si>
+    <t>fg89gxhDJkS9uDGGnGOLCWQABwXy</t>
+  </si>
+  <si>
+    <t>NEW Monthly Report</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:31.577927Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:06:46.3992994Z</t>
+  </si>
+  <si>
+    <t>NOTE: Standard monthly report (spend, leads, MQLs, CPL). September deck is the baseline — review with Michelle before the first formal send-out.</t>
+  </si>
+  <si>
+    <t>[{"id":"bd650b1c3b29455aae63a6023041f987","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define data sources for each section (ad platforms, HubSpot, Salesforce)","orderHint":"85841008685)","lastModifiedDateTime":"2026-10-09T04:27:40.0826982Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"33f6ed52851943bd9cac88d68b9d2c91","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the template (deck or doc)","orderHint":"858410086832","lastModifiedDateTime":"2026-10-09T04:27:49.2959997Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"d350faff36c64c10892efe86caebf449","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Set the recurring monthly deadline","orderHint":"85841008680X*","lastModifiedDateTime":"2026-10-09T04:28:03.2065219Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"e06be6f316b34d3291fd68b63e33e700","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Lock the monthly report structure — spend, leads, MQLs, CPL","orderHint":"8584100868894383159P9","lastModifiedDateTime":"2026-10-09T04:27:36.1056095Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"bd84f59bd3414520a3797bb702af9ea7","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Review with Michelle before first send-out","orderHint":"85841008681%","lastModifiedDateTime":"2026-10-09T04:27:58.7236909Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c5d93028223b450e9865b92320b25bb8","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Populate with September actuals as the baseline","orderHint":"858410086820","lastModifiedDateTime":"2026-10-09T04:54:54.0513122Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121545391216412PC</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:27.5165154Z</t>
+  </si>
+  <si>
+    <t>HW6o9dzYM06ve9xSOE4cCWQAGMF-</t>
+  </si>
+  <si>
+    <t>NEW Weekly Report</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:10.8689354Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:06:36.4582085Z</t>
+  </si>
+  <si>
+    <t>NOTE: Lightweight weekly — spend pacing, leads, key actions. Keep it scannable; set a fixed send day.</t>
+  </si>
+  <si>
+    <t>[{"id":"4e7181aa50a54230ac72a0b8e96e2a2b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Run the first edition this week","orderHint":"8584100867@G","lastModifiedDateTime":"2026-10-09T04:28:25.6918671Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1904b1d8a66543649eca36cf1261165c","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085D?","lastModifiedDateTime":"2026-10-09T04:55:20.6659193Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1e68bdd6a3c1498db37ebb914dd634b7","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085XE","lastModifiedDateTime":"2026-10-09T04:55:09.8212557Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7209ccded82d4b10af8dfa3ceae359a4","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Set the recurring weekly send day","orderHint":"8584100867;-","lastModifiedDateTime":"2026-10-12T00:53:33.6892393Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"69a2d98fc430498c9539990a8e014974","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Automate data pulls where possible","orderHint":"8584100867[L","lastModifiedDateTime":"2026-10-12T00:53:40.9800331Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"6b77d128c7cc42d88f49e5b7dc91477a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Lock the weekly structure — spend pacing, leads, key actions","orderHint":"8584100868521200548P5","lastModifiedDateTime":"2026-10-09T04:28:13.4396393Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ea646136f6104d6da0dab5c97a26c98f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the lightweight template","orderHint":"8584100867I9","lastModifiedDateTime":"2026-10-09T04:28:21.3694981Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121545490581770PJ</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:30.4447498Z</t>
+  </si>
+  <si>
+    <t>BJCaZwDVt0yZHxaD6uURv2QADRAh</t>
+  </si>
+  <si>
+    <t>CX Project</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:02.5773792Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:05:30.6254732Z</t>
+  </si>
+  <si>
+    <t>{"category16":true,"category23":true}</t>
+  </si>
+  <si>
+    <t>CX project:_x000D_
+_x000D_
+NOTE: Customer experience project. Check the vault BrandCom notes for current status.</t>
+  </si>
+  <si>
+    <t>[{"id":"3f0278885ac0479da0ccebf0c2fc3edc","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"List out all SC website links","orderHint":"8584121545910045830P?","lastModifiedDateTime":"2026-10-09T04:35:34.4525344Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"db69dae060104007b422c033dc32d228","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"indexing status.","orderHint":"85841215455O","lastModifiedDateTime":"2026-10-09T04:35:41.3984517Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"78979c11f88041799bb126b7383f8847","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"See if we can implement anything now without budget.","orderHint":"85841215453B","lastModifiedDateTime":"2026-09-15T06:06:12.2625153Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121546148987874PH</t>
+  </si>
+  <si>
+    <t>CX, * Project</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:32.9782539Z</t>
+  </si>
+  <si>
+    <t>b-1JPFpdLEKKfZvGnDoML2QAH-WC</t>
+  </si>
+  <si>
+    <t>Dealer conference Deck</t>
+  </si>
+  <si>
+    <t>Urgent</t>
+  </si>
+  <si>
+    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:08:26.1890146Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
+  </si>
+  <si>
+    <t>2026-09-15T06:04:50.5591925Z</t>
+  </si>
+  <si>
+    <t>2026-09-27T10:00:00Z</t>
+  </si>
+  <si>
+    <t>NOTE: Adam's 20-min Day 2 intro — paid lead gen, capture/nurture, qualification, dealer handover, Salesforce tracking. Align chapter titles with Ivanka's sizzle reel; storyboard locked with Ivanka, Adi, Danni; final deck to Peter Chong. File under C.dealer folder.</t>
+  </si>
+  <si>
+    <t>[{"id":"366250a8ef6b4fbc8fc5ebdd3b7762ea","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Fill in the 'Winning Earlier in the B2B Buying Journey' deck under the C.dealer folder","orderHint":"85841008743F","lastModifiedDateTime":"2026-10-09T06:56:01.9960574Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"38c9999b4bef44a5a75973170e296fde","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Align chapter titles with Ivanka's sizzle reel (outcomes framing)","orderHint":"8584100874X5","lastModifiedDateTime":"2026-10-09T04:56:04.9544382Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"aa81f18f690f43949c4874080497ac1d","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Submit the final Day 2 deck to Peter Chong","orderHint":"85841008746/","lastModifiedDateTime":"2026-10-09T06:55:51.4698494Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"0f71f1ebe5c94be796152f820d92b0f0","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Lock AD station menu format with Danielle","orderHint":"85841006X7","lastModifiedDateTime":"2026-10-12T00:52:49.953366Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2d6fe92109a949d686862fbd999c90c2","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Lock Adam's section: paid lead gen, capture/nurture, qualification, dealer handover, SFDC tracking","orderHint":"8584100875220789081PI","lastModifiedDateTime":"2026-10-09T06:55:36.8215537Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b38224acf6d74d4fa95bbfbcbed4e030","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm the 4-part storyboard flow with Ivanka, Adi and Dani","orderHint":"8584100874E@","lastModifiedDateTime":"2026-10-09T06:55:41.1913823Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"6e06f1120baf443783f0317541aeecf1","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Rehearse the 20-minute interactive intro session","orderHint":"8584100874;&lt;","lastModifiedDateTime":"2026-10-09T04:17:49.2157679Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"3fbed80f82c9420193c51032b968e475","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm Day 1 sizzle video delivery (agency, this weekend)","orderHint":"85841007D","lastModifiedDateTime":"2026-10-09T11:07:45.0422179Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
+  </si>
+  <si>
+    <t>8584121546549580065P9</t>
+  </si>
+  <si>
+    <t>2026-10-14T12:32:36.1502708Z</t>
   </si>
   <si>
     <t>piavqynX0EON-xhZ-CDgAmQAAmxD</t>
@@ -1240,6 +1910,12 @@
     <t>Karman Campaign Kit- Replace Carousel Assets in JP</t>
   </si>
   <si>
+    <t>Gw8d1qlHp0G2XXOqpsiKP2QAPmSt</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
     <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-14T05:56:37.8351868Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
   </si>
   <si>
@@ -1247,6 +1923,9 @@
   </si>
   <si>
     <t>2de20267-3e34-4f36-80b7-993fc93717da</t>
+  </si>
+  <si>
+    <t>2026-10-14T08:56:28.9901566Z</t>
   </si>
   <si>
     <t>Hi Aisah,_x000D_
@@ -1262,674 +1941,7 @@
 3. Keep all file names and other kit content the same.</t>
   </si>
   <si>
-    <t>2026-10-14T08:31:40.3536762Z</t>
-  </si>
-  <si>
-    <t>panY5gjBbEm7WcJFrDSTuWQAIjze</t>
-  </si>
-  <si>
-    <t>Look into audience for LinkedIn based on the GCC file shared</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-07T02:54:01.5391153Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-07T02:54:01.5391739Z</t>
-  </si>
-  <si>
-    <t>8584102653039805165PN</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:31:43.6176175Z</t>
-  </si>
-  <si>
-    <t>lwfxeYVKRkyr1PoDBym412QAKf8F</t>
-  </si>
-  <si>
-    <t>Women of Steel Playlist - Unlisted</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-07T02:13:44.7391879Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-07T02:13:44.7392456Z</t>
-  </si>
-  <si>
-    <t>8584102677207842506P:</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:31:46.5248879Z</t>
-  </si>
-  <si>
-    <t>ZboAyoQAMU2jV6BcqPG12WQAMr-U</t>
-  </si>
-  <si>
-    <t>WorkTech Singapore Social post</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-06T03:11:43.9499892Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-06T03:11:43.950044Z</t>
-  </si>
-  <si>
-    <t>[{"resourceLink":"https://steelcase.sharepoint.com/sites/BrandcomDigitalTeamTaskRequest/Shared%20Documents/ss.jpg","value":{"@odata.type":"#microsoft.graph.plannerExternalReference","alias":"ss.jpg","type":"Other","previewPriority":"8584103504ZJ","lastModifiedDateTime":"2026-10-06T03:13:45.786095Z","lastModifiedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"}}}}]</t>
-  </si>
-  <si>
-    <t>8584103506416161534PI</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:31:49.2566072Z</t>
-  </si>
-  <si>
-    <t>eidBTD4wx0ef5Ew2aIMe1WQAITot</t>
-  </si>
-  <si>
-    <t>Add a banner - all WL pages</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-05T07:18:00.7791066Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-05T07:18:00.7791739Z</t>
-  </si>
-  <si>
-    <t>2026-10-09T10:00:00Z</t>
-  </si>
-  <si>
-    <t>[{"resourceLink":"https://steelcase.sharepoint.com/sites/BrandcomDigitalTeamTaskRequest/Shared%20Documents/1.png","value":{"@odata.type":"#microsoft.graph.plannerExternalReference","alias":"1.png","type":"Other","previewPriority":"8584104221576503676P@","lastModifiedDateTime":"2026-10-05T07:19:47.8621433Z","lastModifiedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"}}}}]</t>
-  </si>
-  <si>
-    <t>8584104222649895193P.</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:31:51.6390913Z</t>
-  </si>
-  <si>
-    <t>ta48yj6nekClG4KtBy5UUWQAIwoT</t>
-  </si>
-  <si>
-    <t>Planning Ideas - Widen</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-01T12:00:39.8045085Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-10-01T12:00:39.8045617Z</t>
-  </si>
-  <si>
-    <t>{"category3":true}</t>
-  </si>
-  <si>
-    <t>8584107509057119924PK</t>
-  </si>
-  <si>
-    <t>Web-Widen</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:31:53.8352151Z</t>
-  </si>
-  <si>
-    <t>0zCmt3_wEUeajg_HWjEu9mQAFNZP</t>
-  </si>
-  <si>
-    <t>To check Hubspot segmentation on users - Digital call</t>
-  </si>
-  <si>
-    <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T07:22:47.3278722Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-30T07:22:47.3279201Z</t>
-  </si>
-  <si>
-    <t>8584108539781878050P&lt;</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:31:56.4243455Z</t>
-  </si>
-  <si>
-    <t>0Di9eFqpfkG1GDPeIxzdl2QABbGp</t>
-  </si>
-  <si>
-    <t>Creating webpages for Work Better 7 articles</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:30:44.9858742Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-30T03:30:44.9859208Z</t>
-  </si>
-  <si>
-    <t>[https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Work%20Better/WB%20Spring%202026%20(WB7%20A%20New%20Mindset)/Translation?csf=1&amp;web=1&amp;e=668MHy](https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Work%20Better/WB%20Spring%202026%20%28WB7%20A%20New%20Mindset%29/Translation?csf=1&amp;amp;web=1&amp;amp;e=668MHy)</t>
-  </si>
-  <si>
-    <t>[{"resourceLink":"https://steelcase.sharepoint.com/sites/BrandcomDigitalTeamTaskRequest/_layouts/15/Doc.aspx?sourcedoc=%7B8E757982-BEA4-4F7C-9545-E4C67FDB4FE5%7D&amp;file=Work%20Better%207%20-%20Articles%20Extraction.xlsx&amp;action=default&amp;mobileredirect=true","value":{"@odata.type":"#microsoft.graph.plannerExternalReference","alias":"Work Better 7 - Articles Extraction.xlsx","type":"Excel","previewPriority":"8584108678569325348P+","lastModifiedDateTime":"2026-09-30T03:31:28.5715201Z","lastModifiedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"}}}}]</t>
-  </si>
-  <si>
-    <t>8584108679005296951P9</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:01.6109520Z</t>
-  </si>
-  <si>
-    <t>Af4lfuRuSkqJ9O-gfRgBHWQAPEPT</t>
-  </si>
-  <si>
-    <t>Migration SE Collection webpage in Japanese</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:28:55.2129923Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-30T03:28:45.9902867Z</t>
-  </si>
-  <si>
-    <t>[https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/JP?d=wc1b139dccfe744978f7591ea11a8b649&amp;csf=1&amp;web=1&amp;e=S9A9B7](https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/JP?d=wc1b139dccfe744978f7591ea11a8b649&amp;amp;csf=1&amp;amp;web=1&amp;amp;e=S9A9B7)</t>
-  </si>
-  <si>
-    <t>8584108680195387782PH</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:04.0421714Z</t>
-  </si>
-  <si>
-    <t>GLcy1eg2bE696YRhutkA32QANKbi</t>
-  </si>
-  <si>
-    <t>Migration SE Collection webpage in Chinese</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:27:43.4234896Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-30T03:27:37.3381237Z</t>
-  </si>
-  <si>
-    <t>[https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/CN?d=wf206f8f1d6aa4affb5c004c9a08f5ba1&amp;csf=1&amp;web=1&amp;e=Jflwbg](https://steelcase.sharepoint.com/:f:/r/sites/ONEMARKETINGAPAC/Shared%20Documents/OneMarketing%20Folder/Brand%20Comms/B.%20Projects/Migration%20SE%20Collection/Translations/CN?d=wf206f8f1d6aa4affb5c004c9a08f5ba1&amp;amp;csf=1&amp;amp;web=1&amp;amp;e=Jflwbg)</t>
-  </si>
-  <si>
-    <t>8584108680882325673PM</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:06.6604324Z</t>
-  </si>
-  <si>
-    <t>IvDVqKsoXkCEQ48JG8edCWQAMSvo</t>
-  </si>
-  <si>
-    <t>HPS external page</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-30T03:22:20.8909643Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-30T03:22:20.8910212Z</t>
-  </si>
-  <si>
-    <t>https://www.steelcase.com/high-performance-seating/</t>
-  </si>
-  <si>
-    <t>8584108684047522812P5</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:10.3524803Z</t>
-  </si>
-  <si>
-    <t>ovv8TGpKtEifKB57xgF6tGQAOkJf</t>
-  </si>
-  <si>
-    <t>Hubspot Segmentation - Japan</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-29T08:37:21.8794304Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-29T08:37:17.0657289Z</t>
-  </si>
-  <si>
-    <t>2026-09-29T10:00:00Z</t>
-  </si>
-  <si>
-    <t>8584109359084977527P2</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:13.0443546Z</t>
-  </si>
-  <si>
-    <t>XdMTSMZ3-0qaTii7SWE_CmQAIdG2</t>
-  </si>
-  <si>
-    <t>ABM Targeting</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:03:01.246682Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-29T06:44:56.7843072Z</t>
-  </si>
-  <si>
-    <t>{"category21":true,"category23":true}</t>
-  </si>
-  <si>
-    <t>NOTE: Building the ABM target list from the 35 APAC priority accounts (shared with Chia May Yee 10/2) layered with Michelle's GCC/SAM list. Files: FY26 Top 35 - GCC.xlsx (SharePoint: OrderLeadTimeAgility &gt; OLTA) and FY26 Master GCC Client List.xlsx (SRNProposalTeam &gt; General). Feeds Gus Wick's tracking one-pager and the LinkedIn Top Companies audience.</t>
-  </si>
-  <si>
-    <t>[{"id":"26d736c3fd5b4b2d9ff8d0b87444e1d1","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Lock the final ABM target list for the media plan","orderHint":"858410087166","lastModifiedDateTime":"2026-10-09T04:22:22.7507964Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"fc50afae2c824e6d890fc8e7bdb7a6fc","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Define tiering criteria (Tier 1/2/3) for targeting intensity","orderHint":"8584100871GJ","lastModifiedDateTime":"2026-10-12T00:52:30.1246544Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"f6b479830461401d9ec2aef14e725c06","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Pull the 35 APAC priority accounts with Chia May Yee","orderHint":"8584100872278331186P-","lastModifiedDateTime":"2026-10-09T04:33:22.1901748Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"064e00fc42e54ba2a8e38840ac058a79","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Layer in the GCC and SAM account list from Michelle","orderHint":"8584100871Z/","lastModifiedDateTime":"2026-10-12T00:52:28.9455031Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"702775ff6aa94eb2b8ad7bb4704aaa2e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Align the account list with Sales (Japan/Korea/India leads)","orderHint":"85841008719I","lastModifiedDateTime":"2026-10-09T04:22:18.5960081Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"0b1e51d75519425e9e7af2fc529344b5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Map accounts to the LinkedIn Top Companies audience","orderHint":"8584100871&gt;L","lastModifiedDateTime":"2026-10-09T04:33:55.2686462Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584109426487303270PN</t>
-  </si>
-  <si>
-    <t>Leadgen, * Project</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:15.9026486Z</t>
-  </si>
-  <si>
-    <t>NPv-ewMX5UOw_bUAhllGJmQAM7n8</t>
-  </si>
-  <si>
-    <t>Gated LPs for consultation, downloads + tracking</t>
-  </si>
-  <si>
-    <t>{"b0dde2c9-92a4-4d86-a4fd-2a130944956f":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-09-29T06:42:39.1644677Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"b0dde2c9-92a4-4d86-a4fd-2a130944956f"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-29T06:42:39.1645232Z</t>
-  </si>
-  <si>
-    <t>2026-10-13T10:00:00Z</t>
-  </si>
-  <si>
-    <t>{"category5":true}</t>
-  </si>
-  <si>
-    <t>Hi Adam, as discussed on Teams, we need a gated landing page for enquiries. This ties in with the offer of "Personalize customization" that we want our audience to eventually fill up. This is specifically for non-lead gen paid campaigns where we need a page to direct audiences to (i.e. eDMs - email nurture series, organic posts). It will also be used in the final email in our email nurture series._x000D_
-Corrine has shared that there was an existing one in the past brand campaign that we can look to use/update: https://www.steelcase.com/asia-en/work-better-campaign/ but if you feel we just need a simpler LP instead of having all these information, feel free to suggest.</t>
-  </si>
-  <si>
-    <t>8584109427863526779P?</t>
-  </si>
-  <si>
-    <t>Email-EDM</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:18.4961657Z</t>
-  </si>
-  <si>
-    <t>6Y4ER53BpU6JV-XbW9HTfmQAPQqq</t>
-  </si>
-  <si>
-    <t>Creative Agency</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:03:08.740805Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-29T06:39:51.7671244Z</t>
-  </si>
-  <si>
-    <t>NOTE: Scoping whether the team needs an external creative agency (campaigns, assets, markets) vs the current WSF setup. Needs Michelle's sign-off on the recommendation.</t>
-  </si>
-  <si>
-    <t>[{"id":"b4d49e3614e1441b9a529d487d3c614e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Shortlist agencies, brief them, collect proposals","orderHint":"85841008713M","lastModifiedDateTime":"2026-10-09T04:22:45.0883122Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"a6b58bda89ac4f6fa058d43d9f7f954e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Evaluate on B2B portfolio, APAC chops, and pricing","orderHint":"858410087127","lastModifiedDateTime":"2026-10-09T04:22:48.9378323Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"39747a22abf84fed9cceb4d2414d7e71","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Recommend and get Michelle's sign-off","orderHint":"85841008711X:","lastModifiedDateTime":"2026-10-09T04:22:52.6383343Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"d9a5a1a68f074f3b940535401072fd37","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Assess the incumbent setup (WSF team) vs external need","orderHint":"858410087152","lastModifiedDateTime":"2026-10-09T04:22:41.0090508Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"bdeeed9b5c3c4813a629de538f2d9336","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410086E","lastModifiedDateTime":"2026-10-09T04:50:43.0304639Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"0343a657e8ae43fca15736bffdcb8608","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define the creative scope — campaigns, assets, markets needed","orderHint":"8584100871895639791P%","lastModifiedDateTime":"2026-10-09T04:22:35.9390415Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584109429537690343P=</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:20.8210173Z</t>
-  </si>
-  <si>
-    <t>furFAgXsvUi5w6PD27OGsGQAFBnP</t>
-  </si>
-  <si>
-    <t>launch new page after form filled in HS</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:04.1091837Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-28T04:11:53.5702771Z</t>
-  </si>
-  <si>
-    <t>Decision: Thank you page is the best_x000D_
-_x000D_
-NOTE: Post-submit experience for HubSpot lead forms — thank-you page vs redirect, with tracking pixels. Critical: test that the Salesforce sync still fires correctly after the redirect is wired.</t>
-  </si>
-  <si>
-    <t>[{"id":"be9a6df72aee420badf777e15057193a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Define the post-submit experience — thank-you page vs redirect","orderHint":"8584100871622563634PB","lastModifiedDateTime":"2026-10-09T04:34:28.5928074Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b26f851fce024b8ea6624295aa69f0e5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft the page copy and CTA","orderHint":"8584100870\\,","lastModifiedDateTime":"2026-10-09T04:23:07.0285872Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"caaa31b72d09433a822b8aecbedd0289","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the page in HubSpot with tracking pixels","orderHint":"8584100870J+","lastModifiedDateTime":"2026-10-09T04:23:11.3012813Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"de0b5014ec9b48d9adc1aef20b5def5d","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Test the full flow — submit, redirect, Salesforce sync intact","orderHint":"8584100870&lt;B","lastModifiedDateTime":"2026-10-09T04:23:24.499444Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"10f8c592845d4b9494efaaf4ee037ec9","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Launch and monitor conversion","orderHint":"85841008709=","lastModifiedDateTime":"2026-10-09T04:23:28.843656Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"a791009c5dac4d1b9185a92b56b19775","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Wire the form to redirect on submit","orderHint":"8584100870A*","lastModifiedDateTime":"2026-10-09T04:23:15.8251031Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584110382319429739PH</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:23.1947870Z</t>
-  </si>
-  <si>
-    <t>iwKT-GjT6kOaJ3JJFD9_z2QAMoie</t>
-  </si>
-  <si>
-    <t>Contentful Project</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:48.730709Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-21T08:13:13.8808502Z</t>
-  </si>
-  <si>
-    <t>NOTE: CMS migration/streamlining work. Check the vault BrandCom notes for current status.</t>
-  </si>
-  <si>
-    <t>[{"id":"231eef543e5541c8b0159d689827db68","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Make deck","orderHint":"8584114691865796372P#","lastModifiedDateTime":"2026-09-23T04:29:18.9150332Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"54a4732733b04da59a9af7409b8b374a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410CF","lastModifiedDateTime":"2026-10-09T04:56:29.426033Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c53910754d59454ab237f8fc1f0db236","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410W.","lastModifiedDateTime":"2026-10-09T04:56:20.5310665Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584116285516486084PE</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:25.5435764Z</t>
-  </si>
-  <si>
-    <t>eWzMNDoXhkqBQpzanbpjzGQAJj7Q</t>
-  </si>
-  <si>
-    <t>Combining Tanya + Lead-Max</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:16.5855687Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-21T06:36:56.7047928Z</t>
-  </si>
-  <si>
-    <t>{"category22":true,"category23":true}</t>
-  </si>
-  <si>
-    <t>Scope out project_x000D_
-_x000D_
-NOTE: Tanya owns Village/digital experience touchpoints; Lead-Max is the B2B lead enrichment flow. Map both and draft a combined scope with owners.</t>
-  </si>
-  <si>
-    <t>[{"id":"74a4b9fc2bdf41268f22a438da9b0b43","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Identify the integration points between the two","orderHint":"8584100870F'","lastModifiedDateTime":"2026-10-09T04:24:04.9098563Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"514abfab9c2e472b8b5a0d005d91d978","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Estimate effort and timeline","orderHint":"858410087073","lastModifiedDateTime":"2026-10-09T04:24:13.6798371Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b4696bf623c34cac87ad5cc6b5e14171","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft the combined scope — objectives, deliverables, owners","orderHint":"8584100870&lt;(","lastModifiedDateTime":"2026-10-09T04:24:08.8920602Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"9dd22e528a4e4a109f10889af81c0bdd","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Map what Tanya owns today (Village, digital experience touchpoints)","orderHint":"8584100871104664726P9","lastModifiedDateTime":"2026-10-09T04:23:55.0320611Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2662bcf3e086434c835b325a62eb6388","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Align with Tanya and get sign-off to proceed","orderHint":"85841008704N","lastModifiedDateTime":"2026-10-09T04:24:18.2767167Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b778f641303e4e6f96d6498a33875faa","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410086/","lastModifiedDateTime":"2026-10-09T04:52:41.0817159Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"58bd9ef32c154bc89f6ac58540da2cca","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Map the Lead-Max flow — enrichment, routing, handover","orderHint":"8584100870Y&gt;","lastModifiedDateTime":"2026-10-09T04:23:58.9520399Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"130a04600f7a4b56b09c7538f3fc7d62","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085Y+","lastModifiedDateTime":"2026-10-09T04:52:49.1404711Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584116343288131154PI</t>
-  </si>
-  <si>
-    <t>Ai, * Project</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:28.4184187Z</t>
-  </si>
-  <si>
-    <t>3atuqLPaoUu7LuKHp43rw2QAIeHI</t>
-  </si>
-  <si>
-    <t>exploring checkin solution for Dani's event.</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:10:09.2109177Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:13:30.1552183Z</t>
-  </si>
-  <si>
-    <t>NOTE: Danni = Danielle Gu. Need a check-in solution (QR / badge printing / walk-ins) for her event — confirm date, venue, headcount with her first.</t>
-  </si>
-  <si>
-    <t>[{"id":"6671ec0e86ec446aa8b9f2dee0bbb4c9","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Shortlist check-in tools and compare","orderHint":"85841008702G","lastModifiedDateTime":"2026-10-09T04:24:36.8418153Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"8e6048f454e949c393be7e472ffeb34a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085EL","lastModifiedDateTime":"2026-10-09T04:53:18.8986374Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c92e1085bf6548a4819d40b7a97a0d3f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Recommend and set up for the event","orderHint":"858410086\\3","lastModifiedDateTime":"2026-10-09T04:24:45.6720052Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"bd3a40a0eefd4db0898f1fd2ee5dbf7d","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm event details with Dani — date, venue, expected headcount","orderHint":"8584100870765289684PG","lastModifiedDateTime":"2026-10-09T04:24:28.9776818Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"4ca61e2f12584b7b98fde744f8ac5d10","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define check-in requirements (QR, badge printing, walk-ins)","orderHint":"85841008704+","lastModifiedDateTime":"2026-10-09T04:24:32.7162704Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"3a8c9267752c4f0fa9135560a0225275","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Test the top option end-to-end","orderHint":"858410087015","lastModifiedDateTime":"2026-10-09T04:24:41.0493597Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121541353582513P8</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:31.0170547Z</t>
-  </si>
-  <si>
-    <t>69DUvv6DpEGI7MvjBPJIVGQAJkXF</t>
-  </si>
-  <si>
-    <t>Sorting out tracking issues Tim Merkel discussion with Katy.</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:10:42.0391989Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:09:01.8563835Z</t>
-  </si>
-  <si>
-    <t>2026-08-18T10:00:00Z</t>
-  </si>
-  <si>
-    <t>{"category13":true,"category23":true}</t>
-  </si>
-  <si>
-    <t>NOTE: Open tracking gaps (UTMs, pixels, CRM sync). Sync with Katy on the paid side first, then bring the issue list to Tim Merkel with agreed owners and fixes.</t>
-  </si>
-  <si>
-    <t>[{"id":"56856271152f468893deffd07fcde6d5","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Hold the discussion and agree owners + fixes","orderHint":"858410086AM","lastModifiedDateTime":"2026-10-09T04:25:15.3755464Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2cef2967e1d5485ebf5522357f1901be","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm reporting is accurate post-fix","orderHint":"858410086;&lt;","lastModifiedDateTime":"2026-10-09T04:25:24.3717245Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ddf5dfd8510e4e9888cca4e337fe07b4","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"List the known tracking issues (UTMs, pixels, CRM sync gaps)","orderHint":"8584100870417444230P$","lastModifiedDateTime":"2026-10-09T04:25:03.7692376Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"18a9d438c6054a79831d9729ced02e24","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Sync with Katy on what's broken on the paid side","orderHint":"858410086\\4","lastModifiedDateTime":"2026-10-09T04:25:07.5179187Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"db92e53e84f048a882b5d80ef33f7330","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Prep the issue list and questions for Tim Merkel","orderHint":"858410086J$","lastModifiedDateTime":"2026-10-09T04:25:11.5096083Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"cadf547371e94b80947f2bc9b01cdf9b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085XO","lastModifiedDateTime":"2026-10-09T04:53:34.7331328Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"8109fee5c5e4401187951ed599f17219","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Implement fixes and verify data flows","orderHint":"858410086=E","lastModifiedDateTime":"2026-10-09T04:25:20.0627738Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c134e7cba5134c8a92e1f6c714272201","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085E\"","lastModifiedDateTime":"2026-10-09T04:53:42.9821417Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121544036796805P&lt;</t>
-  </si>
-  <si>
-    <t>Report, * Project</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:33.7460423Z</t>
-  </si>
-  <si>
-    <t>cnIAqFLCJUGxQosU2Xf8YWQADDv9</t>
-  </si>
-  <si>
-    <t>Create SOP for all processes</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T12:56:39.5506397Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:08:43.4238999Z</t>
-  </si>
-  <si>
-    <t>{"category23":true}</t>
-  </si>
-  <si>
-    <t>NOTE: SOPs for recurring team processes — campaigns, reporting, lead handling, events. Review with Rebecca and Aisah; publish in the shared team folder.</t>
-  </si>
-  <si>
-    <t>[{"id":"aeb87cdbfd25479dbdbbe1fbe166c4e0","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Prioritize by frequency and pain","orderHint":"858410086\\F","lastModifiedDateTime":"2026-10-09T04:35:07.7205755Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2d1a30094481493e94389f4054f1a96e","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Review with Rebecca and Aisah","orderHint":"858410086AJ","lastModifiedDateTime":"2026-10-09T04:25:47.3927311Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ee0597e158d14e169eb8195a5c408d72","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Draft each SOP — steps, owners, tools, templates","orderHint":"858410086JI","lastModifiedDateTime":"2026-10-09T04:25:43.2229748Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7b2d8aae7cdd4ba68425337457cb97f3","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Publish in the shared team folder","orderHint":"858410086=(","lastModifiedDateTime":"2026-10-09T04:25:51.6047727Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"03d22c86c6c543608fc98e4ade5ba651","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Set a quarterly review reminder","orderHint":"858410086;K","lastModifiedDateTime":"2026-10-09T04:25:55.8490471Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7ed5c1db3e53422fa82d5f87e1272035","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Inventory all recurring team processes (campaigns, reporting, lead handling, events)","orderHint":"8584100870100467838P;","lastModifiedDateTime":"2026-10-09T04:25:35.4653589Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121544220929001P5</t>
-  </si>
-  <si>
-    <t>* Project</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:36.0705844Z</t>
-  </si>
-  <si>
-    <t>FRfiIINxl02XF9Di7TUxX2QAPoad</t>
-  </si>
-  <si>
-    <t>AI SDR - Talk to Lim</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:07.4920341Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:08:20.0706731Z</t>
-  </si>
-  <si>
-    <t>NOTE: Lim = Wen Yi Lim (filed the 'Update Lead Times' request 10/5). Align on AI SDR pilot status and next-phase needs. Related vault folder: Ai-SDR/.</t>
-  </si>
-  <si>
-    <t>[{"id":"08b100c3e0a94f1bb7692a9843b71ce0","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085XD","lastModifiedDateTime":"2026-10-09T04:54:00.0335375Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"8f965aa201bc4ad589e654c6e2fcc526","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Action the follow-ups","orderHint":"85841008690X0","lastModifiedDateTime":"2026-10-09T04:26:23.3508937Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"63864ea3dd0947ea88ce78f3266d8b80","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Align on what you need from Lim for the next phase","orderHint":"85841008694M","lastModifiedDateTime":"2026-10-09T04:26:10.7658217Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"932b52c521444ae9a64bd5f6b7dfc11f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Update the Ai-SDR project note with outcomes","orderHint":"85841008691N","lastModifiedDateTime":"2026-10-09T04:26:19.0190685Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"37e2f237e157483d8497601b3a798788","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Prep the AI SDR status — pilot results, call volumes, bookings","orderHint":"8584100869788535167P.","lastModifiedDateTime":"2026-10-09T04:26:06.654577Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"f02d471614fb4c30b291625fe83a26fa","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Hold the discussion and capture decisions","orderHint":"85841008692M","lastModifiedDateTime":"2026-10-09T04:26:14.7999907Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121544454497814P/</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:38.6321877Z</t>
-  </si>
-  <si>
-    <t>IRN2kdT_j0K6rGD7b0_ZuGQAJdXG</t>
-  </si>
-  <si>
-    <t>Replace Clickup with Microsoft Planner</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:44.453109Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:07:48.5565783Z</t>
-  </si>
-  <si>
-    <t>NOTE: Migrating the team's work from ClickUp to Planner (71 tasks in this plan). Task inventory: https://steelcase-my.sharepoint.com/:x:/p/alau2/IQAR4MiHA6b0RK6HK6WoJFngASyjOPeCgRCCeYwcAmUdQnw?e=CBDcl5 — then brief the 8 Brand Comm APAC leaders and archive ClickUp.</t>
-  </si>
-  <si>
-    <t>[{"id":"05106b2ebd064c5badb47aca507ba5a3","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Brief the 8 Brand Comm APAC leaders on the Planner workflow","orderHint":"85841008750ZC","lastModifiedDateTime":"2026-10-09T04:16:19.1515242Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"4e43c9ee7af44a2b8d4ca845cdffd3d2","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Run team training once Michelle green-lights","orderHint":"85841006X6","lastModifiedDateTime":"2026-10-09T11:08:36.3430913Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"9dc535da611945a3a3907b5ac7b7ab9f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"PlannerHub dashboard (go.steelcase.com) shared with Michelle","orderHint":"85841007C","lastModifiedDateTime":"2026-10-09T11:08:31.8750677Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"18ea202c46964c98aa2f1dd8b51d86b7","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Design Planner plan/bucket/label structure to mirror ClickUp","orderHint":"85841008755/","lastModifiedDateTime":"2026-10-09T04:54:19.161359Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"073adbe55c4f40069c32db2b1d9dcba4","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Audit ClickUp - list spaces, lists and open tasks to migrate","orderHint":"8584100875863035531P;","lastModifiedDateTime":"2026-10-09T04:15:59.2088453Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7e39957c813e4b809460af5611f85139","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Recreate buckets and labels in Planner, migrate open tasks","orderHint":"85841008752O","lastModifiedDateTime":"2026-10-09T04:16:11.17932Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"fcaab957a4e7406dbfa0e5945f5646cc","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Re-link key attachments and SharePoint references","orderHint":"85841008751W&amp;","lastModifiedDateTime":"2026-10-09T04:16:15.1992954Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1e224496b9a14de6bf779930567277d8","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm Michelle's monthly/quarterly reporting view, then archive ClickUp","orderHint":"85841008750F1","lastModifiedDateTime":"2026-10-09T04:16:23.1370245Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"3b976c4ed8a545d29b5001bc5f7e99cf","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Export task inventory from ClickUp (assignees, due dates, descriptions)","orderHint":"85841008753K","lastModifiedDateTime":"2026-10-09T04:16:07.5559931Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121544769896651P.</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:42.0376841Z</t>
-  </si>
-  <si>
-    <t>G4J5kNOAxUO_fKW-hi3A-WQABaSH</t>
-  </si>
-  <si>
-    <t>Dashboard: Email reporting</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:23.9117786Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:07:24.7838288Z</t>
-  </si>
-  <si>
-    <t>NOTE: Email performance dashboard from HubSpot data — sends, opens, CTR, leads, MQLs by campaign and market, with MoM trends. Validate against HubSpot native reports.</t>
-  </si>
-  <si>
-    <t>[{"id":"531a64cdae07479a9c60ee02c76e19ae","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define the email KPIs — sends, opens, CTR, leads, MQLs","orderHint":"8584100869293009532PF","lastModifiedDateTime":"2026-10-09T04:26:56.2093928Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"486a17ca4ae14631928e0dd59bd02f44","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Validate numbers against HubSpot's native reports","orderHint":"85841008689O","lastModifiedDateTime":"2026-10-09T04:27:13.4220894Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"920b4ab22f804847aa2eedcd17f8965a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the email performance view by campaign and market","orderHint":"8584100868H6","lastModifiedDateTime":"2026-10-09T04:27:04.5498117Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7ef8279aefd74778ab01a579fcdd4072","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085X3","lastModifiedDateTime":"2026-10-09T04:54:35.5231109Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"aabacd9c521c4589881ba3ace8841f58","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Share with the team and set the refresh cadence","orderHint":"85841008686)","lastModifiedDateTime":"2026-10-09T04:27:22.1613544Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"fb19c7df00b9437eb9346513aa184489","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Add month-on-month trend charts","orderHint":"8584100868&gt;G","lastModifiedDateTime":"2026-10-09T04:27:08.4046179Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ea92e393a940403ab6a05fd32fd276cb","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Connect HubSpot email data to the dashboard source","orderHint":"8584100868Z9","lastModifiedDateTime":"2026-10-09T04:27:00.1394205Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121545007319813PC</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:49.1855271Z</t>
-  </si>
-  <si>
-    <t>fg89gxhDJkS9uDGGnGOLCWQABwXy</t>
-  </si>
-  <si>
-    <t>NEW Monthly Report</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:31.577927Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:06:46.3992994Z</t>
-  </si>
-  <si>
-    <t>NOTE: Standard monthly report (spend, leads, MQLs, CPL). September deck is the baseline — review with Michelle before the first formal send-out.</t>
-  </si>
-  <si>
-    <t>[{"id":"bd650b1c3b29455aae63a6023041f987","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Define data sources for each section (ad platforms, HubSpot, Salesforce)","orderHint":"85841008685)","lastModifiedDateTime":"2026-10-09T04:27:40.0826982Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"33f6ed52851943bd9cac88d68b9d2c91","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the template (deck or doc)","orderHint":"858410086832","lastModifiedDateTime":"2026-10-09T04:27:49.2959997Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"d350faff36c64c10892efe86caebf449","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Set the recurring monthly deadline","orderHint":"85841008680X*","lastModifiedDateTime":"2026-10-09T04:28:03.2065219Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"e06be6f316b34d3291fd68b63e33e700","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Lock the monthly report structure — spend, leads, MQLs, CPL","orderHint":"8584100868894383159P9","lastModifiedDateTime":"2026-10-09T04:27:36.1056095Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"bd84f59bd3414520a3797bb702af9ea7","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Review with Michelle before first send-out","orderHint":"85841008681%","lastModifiedDateTime":"2026-10-09T04:27:58.7236909Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"c5d93028223b450e9865b92320b25bb8","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Populate with September actuals as the baseline","orderHint":"858410086820","lastModifiedDateTime":"2026-10-09T04:54:54.0513122Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121545391216412PC</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:53.0128542Z</t>
-  </si>
-  <si>
-    <t>HW6o9dzYM06ve9xSOE4cCWQAGMF-</t>
-  </si>
-  <si>
-    <t>NEW Weekly Report</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:09:10.8689354Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:06:36.4582085Z</t>
-  </si>
-  <si>
-    <t>NOTE: Lightweight weekly — spend pacing, leads, key actions. Keep it scannable; set a fixed send day.</t>
-  </si>
-  <si>
-    <t>[{"id":"4e7181aa50a54230ac72a0b8e96e2a2b","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Run the first edition this week","orderHint":"8584100867@G","lastModifiedDateTime":"2026-10-09T04:28:25.6918671Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1904b1d8a66543649eca36cf1261165c","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Initial context gathered from vault and team chats","orderHint":"858410085D?","lastModifiedDateTime":"2026-10-09T04:55:20.6659193Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"1e68bdd6a3c1498db37ebb914dd634b7","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Task scoped and added to Planner","orderHint":"858410085XE","lastModifiedDateTime":"2026-10-09T04:55:09.8212557Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"7209ccded82d4b10af8dfa3ceae359a4","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Set the recurring weekly send day","orderHint":"8584100867;-","lastModifiedDateTime":"2026-10-12T00:53:33.6892393Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"69a2d98fc430498c9539990a8e014974","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Automate data pulls where possible","orderHint":"8584100867[L","lastModifiedDateTime":"2026-10-12T00:53:40.9800331Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"6b77d128c7cc42d88f49e5b7dc91477a","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Lock the weekly structure — spend pacing, leads, key actions","orderHint":"8584100868521200548P5","lastModifiedDateTime":"2026-10-09T04:28:13.4396393Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"ea646136f6104d6da0dab5c97a26c98f","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Build the lightweight template","orderHint":"8584100867I9","lastModifiedDateTime":"2026-10-09T04:28:21.3694981Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121545490581770PJ</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:56.4219381Z</t>
-  </si>
-  <si>
-    <t>BJCaZwDVt0yZHxaD6uURv2QADRAh</t>
-  </si>
-  <si>
-    <t>CX Project</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:13:02.5773792Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:05:30.6254732Z</t>
-  </si>
-  <si>
-    <t>{"category16":true,"category23":true}</t>
-  </si>
-  <si>
-    <t>CX project:_x000D_
-_x000D_
-NOTE: Customer experience project. Check the vault BrandCom notes for current status.</t>
-  </si>
-  <si>
-    <t>[{"id":"3f0278885ac0479da0ccebf0c2fc3edc","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"List out all SC website links","orderHint":"8584121545910045830P?","lastModifiedDateTime":"2026-10-09T04:35:34.4525344Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"db69dae060104007b422c033dc32d228","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"indexing status.","orderHint":"85841215455O","lastModifiedDateTime":"2026-10-09T04:35:41.3984517Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"78979c11f88041799bb126b7383f8847","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"See if we can implement anything now without budget.","orderHint":"85841215453B","lastModifiedDateTime":"2026-09-15T06:06:12.2625153Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121546148987874PH</t>
-  </si>
-  <si>
-    <t>CX, * Project</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:32:59.3085054Z</t>
-  </si>
-  <si>
-    <t>b-1JPFpdLEKKfZvGnDoML2QAH-WC</t>
-  </si>
-  <si>
-    <t>Dealer conference Deck</t>
-  </si>
-  <si>
-    <t>Urgent</t>
-  </si>
-  <si>
-    <t>{"129b8133-2f40-46f4-8391-49fec10f3174":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-08T13:08:26.1890146Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
-  </si>
-  <si>
-    <t>2026-09-15T06:04:50.5591925Z</t>
-  </si>
-  <si>
-    <t>2026-09-27T10:00:00Z</t>
-  </si>
-  <si>
-    <t>NOTE: Adam's 20-min Day 2 intro — paid lead gen, capture/nurture, qualification, dealer handover, Salesforce tracking. Align chapter titles with Ivanka's sizzle reel; storyboard locked with Ivanka, Adi, Danni; final deck to Peter Chong. File under C.dealer folder.</t>
-  </si>
-  <si>
-    <t>[{"id":"366250a8ef6b4fbc8fc5ebdd3b7762ea","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Fill in the 'Winning Earlier in the B2B Buying Journey' deck under the C.dealer folder","orderHint":"85841008743F","lastModifiedDateTime":"2026-10-09T06:56:01.9960574Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"38c9999b4bef44a5a75973170e296fde","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Align chapter titles with Ivanka's sizzle reel (outcomes framing)","orderHint":"8584100874X5","lastModifiedDateTime":"2026-10-09T04:56:04.9544382Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"aa81f18f690f43949c4874080497ac1d","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Submit the final Day 2 deck to Peter Chong","orderHint":"85841008746/","lastModifiedDateTime":"2026-10-09T06:55:51.4698494Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"0f71f1ebe5c94be796152f820d92b0f0","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Lock AD station menu format with Danielle","orderHint":"85841006X7","lastModifiedDateTime":"2026-10-12T00:52:49.953366Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"2d6fe92109a949d686862fbd999c90c2","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":true,"title":"Lock Adam's section: paid lead gen, capture/nurture, qualification, dealer handover, SFDC tracking","orderHint":"8584100875220789081PI","lastModifiedDateTime":"2026-10-09T06:55:36.8215537Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"b38224acf6d74d4fa95bbfbcbed4e030","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm the 4-part storyboard flow with Ivanka, Adi and Dani","orderHint":"8584100874E@","lastModifiedDateTime":"2026-10-09T06:55:41.1913823Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"6e06f1120baf443783f0317541aeecf1","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Rehearse the 20-minute interactive intro session","orderHint":"8584100874;&lt;","lastModifiedDateTime":"2026-10-09T04:17:49.2157679Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}},{"id":"3fbed80f82c9420193c51032b968e475","value":{"@odata.type":"#microsoft.graph.plannerChecklistItem","isChecked":false,"title":"Confirm Day 1 sizzle video delivery (agency, this weekend)","orderHint":"85841007D","lastModifiedDateTime":"2026-10-09T11:07:45.0422179Z","lastModifiedBy":{"user":{"displayName":null,"id":"129b8133-2f40-46f4-8391-49fec10f3174"}}}}]</t>
-  </si>
-  <si>
-    <t>8584121546549580065P9</t>
-  </si>
-  <si>
-    <t>2026-10-14T08:33:02.2613134Z</t>
+    <t>2026-10-14T12:32:38.6947186Z</t>
   </si>
   <si>
     <t>L0XrZbCjs0iGjNEkBsSAFGQAEO-T</t>
@@ -1938,12 +1950,6 @@
     <t>Double check if HK will still go live</t>
   </si>
   <si>
-    <t>Gw8d1qlHp0G2XXOqpsiKP2QAPmSt</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
     <t>{"d8b70168-3e9f-451c-898e-9a1da643aafe":{"@odata.type":"#microsoft.graph.plannerAssignment","assignedDateTime":"2026-10-09T02:47:47.7229121Z","orderHint":"\"","assignedBy":{"user":{"displayName":null,"id":"d8b70168-3e9f-451c-898e-9a1da643aafe"},"application":{"displayName":null,"id":"75f31797-37c9-498e-8dc9-53c16a36afca"}}}}</t>
   </si>
   <si>
@@ -1956,7 +1962,7 @@
     <t>8584100928777981074P0</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:04.6437125Z</t>
+    <t>2026-10-14T12:32:42.5876900Z</t>
   </si>
   <si>
     <t>W2PVHGlZvEaIMecOH-Jg7GQAIWKQ</t>
@@ -1990,7 +1996,7 @@
     <t>8584101832698446128P/</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:07.1509590Z</t>
+    <t>2026-10-14T12:32:44.7345017Z</t>
   </si>
   <si>
     <t>ncyb0qG09kaMtGqO6eX3TWQAMc3i</t>
@@ -2014,7 +2020,7 @@
     <t>8584101776170751046P'</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:10.0311167Z</t>
+    <t>2026-10-14T12:32:47.4443794Z</t>
   </si>
   <si>
     <t>NfvvcewVtUqpSF6JsAoibWQAMAxg</t>
@@ -2047,7 +2053,7 @@
     <t>2026-10-07; 2026-10-07</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:12.3755977Z</t>
+    <t>2026-10-14T12:32:51.1076151Z</t>
   </si>
   <si>
     <t>hlp_qY7gCkiM0frt-hDWj2QAOmhE</t>
@@ -2083,7 +2089,7 @@
     <t>8584107422838280886P9</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:14.6109756Z</t>
+    <t>2026-10-14T12:32:53.9873551Z</t>
   </si>
   <si>
     <t>YaYExzpOb0K9JxzQIY9EhWQAL95c</t>
@@ -2110,7 +2116,7 @@
     <t>8584108705946125597P"</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:16.9319829Z</t>
+    <t>2026-10-14T12:32:56.6577520Z</t>
   </si>
   <si>
     <t>HIchy-JP_EWjwiZYNoxudGQACq63</t>
@@ -2147,7 +2153,7 @@
     <t>8584101775375270877P9</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:20.0095115Z</t>
+    <t>2026-10-14T12:32:59.0180431Z</t>
   </si>
   <si>
     <t>HkGPawKTzky72t8qfY8DnmQAKJUn</t>
@@ -2171,7 +2177,7 @@
     <t>8584098172761542889P6</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:22.4484629Z</t>
+    <t>2026-10-14T12:33:01.2132535Z</t>
   </si>
   <si>
     <t>3-3Vuy0Pck2MOtnlUS5B4WQALJ9u</t>
@@ -2192,7 +2198,7 @@
     <t>8584098350691109044P?</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:24.9877158Z</t>
+    <t>2026-10-14T12:33:05.0875458Z</t>
   </si>
   <si>
     <t>08NByjMNHUuDuM7gnT-J3mQAJQf4</t>
@@ -2213,7 +2219,7 @@
     <t>8584098362306512470P=</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:27.1598029Z</t>
+    <t>2026-10-14T12:33:07.5776066Z</t>
   </si>
   <si>
     <t>mSaj-JmQMkGP77Y5UWUN4WQAFG4a</t>
@@ -2234,7 +2240,7 @@
     <t>8584101804946102014P&lt;</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:29.8912161Z</t>
+    <t>2026-10-14T12:33:10.1056662Z</t>
   </si>
   <si>
     <t>6Z6GkD2jD0yQxfo9CZJpqGQAPiSn</t>
@@ -2255,7 +2261,7 @@
     <t>8584100800379242312PI</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:32.2863022Z</t>
+    <t>2026-10-14T12:33:12.4930412Z</t>
   </si>
   <si>
     <t>5yfrD52cFku6PRIWcohRHGQAGN5D</t>
@@ -2276,7 +2282,7 @@
     <t>8584101664271308679P4</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:34.6689134Z</t>
+    <t>2026-10-14T12:33:15.6337239Z</t>
   </si>
   <si>
     <t>pp2z6VEuQUmPMUDrwMCRfGQAI_76</t>
@@ -2319,7 +2325,7 @@
     <t>8584108597307199579P*</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:36.7879077Z</t>
+    <t>2026-10-14T12:33:18.2440914Z</t>
   </si>
   <si>
     <t>miHghbSOHUqoA8hgPGCPrWQALFly</t>
@@ -2340,7 +2346,7 @@
     <t>8584100829347170980P&gt;</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:38.8473286Z</t>
+    <t>2026-10-14T12:33:21.1706938Z</t>
   </si>
   <si>
     <t>BjzuTCwKkUuyvpFTZgMC0mQADPsh</t>
@@ -2361,7 +2367,7 @@
     <t>8584100918300154262P)</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:41.9371837Z</t>
+    <t>2026-10-14T12:33:23.9299712Z</t>
   </si>
   <si>
     <t>NTWZp_rCf0SmTzpTfcXw2mQAMgvf</t>
@@ -2388,7 +2394,7 @@
     <t>2026-10-09; 2026-10-08</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:44.6611952Z</t>
+    <t>2026-10-14T12:33:29.6644396Z</t>
   </si>
   <si>
     <t>avgDEXA0rU2sGjeUyHFtMWQACUld</t>
@@ -2412,7 +2418,7 @@
     <t>8584101808112006160PG</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:47.1080069Z</t>
+    <t>2026-10-14T12:33:31.8535071Z</t>
   </si>
   <si>
     <t>Z8eNJLmk4Uyh4caBeaQ91mQAOeef</t>
@@ -2448,7 +2454,7 @@
     <t>Email-APAnnouncement</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:50.3460863Z</t>
+    <t>2026-10-14T12:33:34.0767581Z</t>
   </si>
   <si>
     <t>RV709phnUUyrHhJvXA7TFGQAIlUY</t>
@@ -2486,7 +2492,7 @@
     <t>Leadgen</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:53.1639039Z</t>
+    <t>2026-10-14T12:33:36.7204385Z</t>
   </si>
   <si>
     <t>DWvhU28erUy_yb_KjYyRG2QAH2Z8</t>
@@ -2522,7 +2528,7 @@
     <t>ADS- Planning, * Project</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:55.5524898Z</t>
+    <t>2026-10-14T12:33:40.6978122Z</t>
   </si>
   <si>
     <t>s30OqpDkO0Soz6yzOrzfwmQAB0wA</t>
@@ -2552,7 +2558,7 @@
     <t>8584116230485580608PJ</t>
   </si>
   <si>
-    <t>2026-10-14T08:33:57.7786442Z</t>
+    <t>2026-10-14T12:33:44.7463914Z</t>
   </si>
   <si>
     <t>B7d_DawnlUWTx5mkf1mtN2QAGfdr</t>
@@ -2573,7 +2579,7 @@
     <t>8584101632329630668P=</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:00.1567358Z</t>
+    <t>2026-10-14T12:33:47.4315814Z</t>
   </si>
   <si>
     <t>m-P8J6jUH0uQlcbBkMtabGQAIWhk</t>
@@ -2594,7 +2600,7 @@
     <t>8584104240431303701P9</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:02.3204209Z</t>
+    <t>2026-10-14T12:33:51.3908288Z</t>
   </si>
   <si>
     <t>gmhykCfrLkuCjABKj2cx4WQAONX5</t>
@@ -2626,7 +2632,7 @@
     <t>8584108707163160908P6</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:04.4576720Z</t>
+    <t>2026-10-14T12:33:54.7646971Z</t>
   </si>
   <si>
     <t>BqmHqCbGCEG7edCXES4G-WQAEbIG</t>
@@ -2647,7 +2653,7 @@
     <t>8584102534789372856P8</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:06.6833772Z</t>
+    <t>2026-10-14T12:33:56.9199233Z</t>
   </si>
   <si>
     <t>IZ7DX3qlUU-4VxFrAZfMTWQAFsR7</t>
@@ -2674,7 +2680,7 @@
     <t>8584104157904163031PD</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:09.0416829Z</t>
+    <t>2026-10-14T12:34:09.8564515Z</t>
   </si>
   <si>
     <t>waYst9GvmEmtvfQkkSQP6WQANpWq</t>
@@ -2695,7 +2701,7 @@
     <t>8584102652174433955P&gt;</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:11.9173915Z</t>
+    <t>2026-10-14T12:34:12.1285374Z</t>
   </si>
   <si>
     <t>u734iKBrHEyIRSoQv53MHWQAMxcE</t>
@@ -2722,7 +2728,7 @@
     <t>8584102464088232931PO</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:14.3352487Z</t>
+    <t>2026-10-14T12:34:15.3281709Z</t>
   </si>
   <si>
     <t>7xL5TnIKu0uCoSnHC1ahkmQAOowe</t>
@@ -2743,7 +2749,7 @@
     <t>8584102286131730573P2</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:16.5165422Z</t>
+    <t>2026-10-14T12:34:17.6019438Z</t>
   </si>
   <si>
     <t>5ftjnlh23UyiWayOpSDgUmQADNWi</t>
@@ -2764,7 +2770,7 @@
     <t>8584102672619284044P:</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:18.6836061Z</t>
+    <t>2026-10-14T12:34:20.4330537Z</t>
   </si>
   <si>
     <t>8T2xCHtA9ES2m7m0VQiEU2QADfNj</t>
@@ -2817,7 +2823,7 @@
     <t>Report</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:20.8406306Z</t>
+    <t>2026-10-14T12:34:22.9371716Z</t>
   </si>
   <si>
     <t>pDG3Z3mAQEunRpbulbkaMWQAD_gX</t>
@@ -2838,7 +2844,7 @@
     <t>8584103388303990653P=</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:23.7737365Z</t>
+    <t>2026-10-14T12:34:26.0112269Z</t>
   </si>
   <si>
     <t>qjbQqFW3rkqU_Y71aNLN0GQAMpk1</t>
@@ -2862,7 +2868,7 @@
     <t>2026-10-09; 2026-09-30</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:26.1192893Z</t>
+    <t>2026-10-14T12:34:28.5067976Z</t>
   </si>
   <si>
     <t>PuPnGUyE_06atzpo7qV2OGQAIMAJ</t>
@@ -2883,7 +2889,7 @@
     <t>8584103507284463031P(</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:28.6161274Z</t>
+    <t>2026-10-14T12:34:31.0628254Z</t>
   </si>
   <si>
     <t>YeY3NDAxIUOwj1HyC1VzpGQAE0Bo</t>
@@ -2917,7 +2923,7 @@
 Timeline &amp; Priority:</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:31.1186644Z</t>
+    <t>2026-10-14T12:34:33.7710327Z</t>
   </si>
   <si>
     <t>ype12aslxkiLzsDC8N4tLmQAGSij</t>
@@ -2945,7 +2951,7 @@
 Timeline &amp; Priority:</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:33.6478979Z</t>
+    <t>2026-10-14T12:34:36.4613279Z</t>
   </si>
   <si>
     <t>HrtdnEzxQEKAcc3pzkqMNWQAGAjq</t>
@@ -2966,7 +2972,7 @@
     <t>8584104265615655243P5</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:36.8875830Z</t>
+    <t>2026-10-14T12:34:38.7511951Z</t>
   </si>
   <si>
     <t>VxeEf5JfcUiIv88yy3TSUWQAG5vw</t>
@@ -2987,7 +2993,7 @@
     <t>8584104247297198655P6</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:39.4847521Z</t>
+    <t>2026-10-14T12:34:41.7846500Z</t>
   </si>
   <si>
     <t>QF_jvYONe0GchSWWj5sQlWQAEBGG</t>
@@ -3008,7 +3014,7 @@
     <t>8584106969262518186PD</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:42.3596181Z</t>
+    <t>2026-10-14T12:34:44.5198424Z</t>
   </si>
   <si>
     <t>OCBv-4qopE2_ufT6qTveiGQAAhhY</t>
@@ -3029,7 +3035,7 @@
     <t>8584106968798242200P;</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:44.6962708Z</t>
+    <t>2026-10-14T12:34:47.1298829Z</t>
   </si>
   <si>
     <t>PU0u1ATdXU6DdTaKm_70U2QAMEp7</t>
@@ -3060,7 +3066,7 @@
     <t>8584108710323359809P&amp;</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:48.3077718Z</t>
+    <t>2026-10-14T12:34:49.9508626Z</t>
   </si>
   <si>
     <t>0tgMR7oA_kes_VePN6yB7GQAO7d4</t>
@@ -3100,7 +3106,7 @@
     <t>8584107504577091647PE</t>
   </si>
   <si>
-    <t>2026-10-14T08:34:51.1024512Z</t>
+    <t>2026-10-14T12:34:53.1196979Z</t>
   </si>
   <si>
     <t>0w9XW1ps9kOMurnzSQ20ymQADJVF</t>
@@ -4776,10 +4782,10 @@
         <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -4791,10 +4797,10 @@
         <v>40</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>96</v>
@@ -4804,7 +4810,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R12" s="2" t="b">
         <v>0</v>
@@ -4814,7 +4820,7 @@
         <v>2</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
@@ -4823,7 +4829,7 @@
         <v>45</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2" t="s">
@@ -4833,7 +4839,7 @@
         <v>48</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC12" s="3">
         <v>46307</v>
@@ -4861,13 +4867,13 @@
     </row>
     <row r="13" spans="1:34" ht="15" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>37</v>
@@ -4888,10 +4894,10 @@
         <v>40</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>43</v>
@@ -4901,7 +4907,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R13" s="2" t="b">
         <v>0</v>
@@ -4920,7 +4926,7 @@
         <v>45</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2" t="s">
@@ -4930,7 +4936,7 @@
         <v>48</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AC13" s="3">
         <v>46307</v>
@@ -4958,13 +4964,13 @@
     </row>
     <row r="14" spans="1:34" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>37</v>
@@ -4988,7 +4994,7 @@
         <v>67</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>96</v>
@@ -5017,7 +5023,7 @@
         <v>45</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
@@ -5049,13 +5055,13 @@
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>37</v>
@@ -5076,10 +5082,10 @@
         <v>40</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>96</v>
@@ -5089,7 +5095,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R15" s="2" t="b">
         <v>0</v>
@@ -5108,7 +5114,7 @@
         <v>45</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2" t="s">
@@ -5118,7 +5124,7 @@
         <v>48</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AC15" s="3">
         <v>46304</v>
@@ -5146,13 +5152,13 @@
     </row>
     <row r="16" spans="1:34" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>37</v>
@@ -5173,10 +5179,10 @@
         <v>40</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>96</v>
@@ -5205,7 +5211,7 @@
         <v>45</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2" t="s">
@@ -5243,13 +5249,13 @@
     </row>
     <row r="17" spans="1:34" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>37</v>
@@ -5270,10 +5276,10 @@
         <v>40</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>96</v>
@@ -5283,7 +5289,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R17" s="2" t="b">
         <v>0</v>
@@ -5293,7 +5299,7 @@
         <v>5</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -5302,7 +5308,7 @@
         <v>45</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2" t="s">
@@ -5312,7 +5318,7 @@
         <v>48</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AC17" s="3">
         <v>46304</v>
@@ -5340,13 +5346,13 @@
     </row>
     <row r="18" spans="1:34" ht="15" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>37</v>
@@ -5367,10 +5373,10 @@
         <v>40</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>96</v>
@@ -5380,7 +5386,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R18" s="2" t="b">
         <v>0</v>
@@ -5399,7 +5405,7 @@
         <v>45</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" s="2" t="s">
@@ -5409,7 +5415,7 @@
         <v>48</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AC18" s="3">
         <v>46304</v>
@@ -5437,22 +5443,22 @@
     </row>
     <row r="19" spans="1:34" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -5464,28 +5470,28 @@
         <v>40</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>96</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R19" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="T19" s="2">
         <v>0</v>
@@ -5510,7 +5516,7 @@
         <v>48</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC19" s="3">
         <v>46308</v>
@@ -5538,13 +5544,13 @@
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>37</v>
@@ -5565,17 +5571,17 @@
         <v>40</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -5599,7 +5605,7 @@
         <v>45</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" s="2" t="s">
@@ -5635,13 +5641,13 @@
     </row>
     <row r="21" spans="1:34" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>37</v>
@@ -5662,10 +5668,10 @@
         <v>40</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>43</v>
@@ -5675,7 +5681,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R21" s="2" t="b">
         <v>0</v>
@@ -5694,7 +5700,7 @@
         <v>45</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" s="2" t="s">
@@ -5704,7 +5710,7 @@
         <v>48</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC21" s="3">
         <v>46304</v>
@@ -5732,22 +5738,22 @@
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -5759,10 +5765,10 @@
         <v>40</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>43</v>
@@ -5791,7 +5797,7 @@
         <v>45</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" s="2" t="s">
@@ -5829,13 +5835,13 @@
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>37</v>
@@ -5856,34 +5862,34 @@
         <v>40</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>96</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R23" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="T23" s="2">
         <v>6</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="V23" s="2">
         <v>0</v>
@@ -5892,7 +5898,7 @@
         <v>45</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2" t="s">
@@ -5902,7 +5908,7 @@
         <v>48</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AC23" s="3">
         <v>46304</v>
@@ -5930,22 +5936,22 @@
     </row>
     <row r="24" spans="1:34" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -6069,7 +6075,7 @@
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R25" s="2" t="b">
         <v>1</v>
@@ -6100,7 +6106,7 @@
         <v>48</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AC25" s="3">
         <v>46304</v>
@@ -6168,7 +6174,7 @@
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R26" s="2" t="b">
         <v>1</v>
@@ -6199,7 +6205,7 @@
         <v>48</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AC26" s="3">
         <v>46304</v>
@@ -6462,7 +6468,7 @@
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -6732,10 +6738,10 @@
         <v>37</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
@@ -7023,10 +7029,10 @@
         <v>37</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
@@ -7120,10 +7126,10 @@
         <v>37</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
@@ -7217,10 +7223,10 @@
         <v>37</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
@@ -7314,10 +7320,10 @@
         <v>37</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
@@ -7411,10 +7417,10 @@
         <v>37</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
@@ -7611,10 +7617,10 @@
         <v>37</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
@@ -7708,10 +7714,10 @@
         <v>37</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -7805,10 +7811,10 @@
         <v>37</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
@@ -7902,10 +7908,10 @@
         <v>37</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
@@ -7930,7 +7936,7 @@
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R44" s="2" t="b">
         <v>0</v>
@@ -7959,7 +7965,7 @@
         <v>48</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC44" s="3">
         <v>46303</v>
@@ -7999,10 +8005,10 @@
         <v>37</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
@@ -8098,10 +8104,10 @@
         <v>37</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
@@ -8119,23 +8125,19 @@
         <v>399</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>400</v>
+        <v>43</v>
       </c>
       <c r="M46" s="2"/>
-      <c r="N46" s="2" t="s">
-        <v>216</v>
-      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="R46" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S46" s="2" t="s">
-        <v>401</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S46" s="2"/>
       <c r="T46" s="2">
         <v>0</v>
       </c>
@@ -8148,19 +8150,21 @@
       <c r="W46" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="X46" s="2">
-        <v>8584101831</v>
+      <c r="X46" s="2" t="s">
+        <v>400</v>
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" s="2" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="AA46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB46" s="2"/>
+      <c r="AB46" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="AC46" s="3">
-        <v>46309</v>
+        <v>46302</v>
       </c>
       <c r="AD46" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -8172,35 +8176,35 @@
       </c>
       <c r="AF46" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG46" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>2</v>
-      </c>
-      <c r="AH46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-2</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="1:34" ht="15" customHeight="1">
       <c r="A47" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
@@ -8212,10 +8216,10 @@
         <v>40</v>
       </c>
       <c r="J47" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K47" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>43</v>
@@ -8225,7 +8229,7 @@
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="R47" s="2" t="b">
         <v>0</v>
@@ -8244,7 +8248,7 @@
         <v>45</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" s="2" t="s">
@@ -8253,9 +8257,7 @@
       <c r="AA47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB47" s="2" t="s">
-        <v>143</v>
-      </c>
+      <c r="AB47" s="2"/>
       <c r="AC47" s="3">
         <v>46302</v>
       </c>
@@ -8282,22 +8284,22 @@
     </row>
     <row r="48" spans="1:34" ht="15" customHeight="1">
       <c r="A48" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
@@ -8309,10 +8311,10 @@
         <v>40</v>
       </c>
       <c r="J48" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K48" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>43</v>
@@ -8322,7 +8324,7 @@
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2" t="s">
-        <v>67</v>
+        <v>360</v>
       </c>
       <c r="R48" s="2" t="b">
         <v>0</v>
@@ -8335,10 +8337,10 @@
         <v>45</v>
       </c>
       <c r="V48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>45</v>
+        <v>412</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>413</v>
@@ -8350,9 +8352,11 @@
       <c r="AA48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB48" s="2"/>
+      <c r="AB48" s="2" t="s">
+        <v>362</v>
+      </c>
       <c r="AC48" s="3">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="AD48" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -8389,10 +8393,10 @@
         <v>37</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>207</v>
+        <v>75</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
@@ -8410,14 +8414,16 @@
         <v>418</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>43</v>
+        <v>390</v>
       </c>
       <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
+      <c r="N49" s="2" t="s">
+        <v>419</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>360</v>
+        <v>186</v>
       </c>
       <c r="R49" s="2" t="b">
         <v>0</v>
@@ -8433,23 +8439,23 @@
         <v>1</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="AA49" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>362</v>
+        <v>188</v>
       </c>
       <c r="AC49" s="3">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="AD49" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -8467,29 +8473,29 @@
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
         <v>0</v>
       </c>
-      <c r="AH49" s="4" t="str">
+      <c r="AH49" s="4">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:34" ht="15" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
@@ -8501,22 +8507,22 @@
         <v>40</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="2" t="s">
-        <v>184</v>
+        <v>427</v>
       </c>
       <c r="R50" s="2" t="b">
         <v>0</v>
@@ -8529,10 +8535,10 @@
         <v>45</v>
       </c>
       <c r="V50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>427</v>
+        <v>45</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>428</v>
@@ -8545,10 +8551,10 @@
         <v>48</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>186</v>
+        <v>429</v>
       </c>
       <c r="AC50" s="3">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="AD50" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -8560,26 +8566,26 @@
       </c>
       <c r="AF50" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG50" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH50" s="4">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:34" ht="15" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>37</v>
@@ -8600,22 +8606,20 @@
         <v>40</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>390</v>
+        <v>43</v>
       </c>
       <c r="M51" s="2"/>
-      <c r="N51" s="2" t="s">
-        <v>426</v>
-      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="2" t="s">
-        <v>434</v>
+        <v>307</v>
       </c>
       <c r="R51" s="2" t="b">
         <v>0</v>
@@ -8638,16 +8642,16 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" s="2" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="AA51" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB51" s="2" t="s">
-        <v>436</v>
+        <v>309</v>
       </c>
       <c r="AC51" s="3">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="AD51" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -8659,38 +8663,38 @@
       </c>
       <c r="AF51" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG51" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>5</v>
-      </c>
-      <c r="AH51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-5</v>
+        <v/>
       </c>
     </row>
     <row r="52" spans="1:34" ht="15" customHeight="1">
       <c r="A52" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G52" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H52" s="2">
         <v>5</v>
@@ -8699,25 +8703,29 @@
         <v>40</v>
       </c>
       <c r="J52" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>441</v>
-      </c>
       <c r="L52" s="2" t="s">
-        <v>43</v>
+        <v>390</v>
       </c>
       <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
+      <c r="N52" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2" t="s">
-        <v>307</v>
+        <v>186</v>
       </c>
       <c r="R52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="T52" s="2">
         <v>0</v>
       </c>
@@ -8725,23 +8733,23 @@
         <v>45</v>
       </c>
       <c r="V52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>45</v>
+        <v>442</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="AA52" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="AC52" s="3">
         <v>46295</v>
@@ -8762,29 +8770,29 @@
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
         <v>0</v>
       </c>
-      <c r="AH52" s="4" t="str">
+      <c r="AH52" s="4">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="G53" s="2">
         <v>50</v>
@@ -8796,28 +8804,28 @@
         <v>40</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R53" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="T53" s="2">
         <v>0</v>
@@ -8826,13 +8834,13 @@
         <v>45</v>
       </c>
       <c r="V53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>449</v>
+        <v>45</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" s="2" t="s">
@@ -8842,7 +8850,7 @@
         <v>48</v>
       </c>
       <c r="AB53" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC53" s="3">
         <v>46295</v>
@@ -8870,22 +8878,22 @@
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>207</v>
+        <v>75</v>
       </c>
       <c r="G54" s="2">
         <v>50</v>
@@ -8897,28 +8905,28 @@
         <v>40</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2" t="s">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="R54" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="T54" s="2">
         <v>0</v>
@@ -8933,7 +8941,7 @@
         <v>45</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" s="2" t="s">
@@ -8942,9 +8950,7 @@
       <c r="AA54" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB54" s="2" t="s">
-        <v>186</v>
-      </c>
+      <c r="AB54" s="2"/>
       <c r="AC54" s="3">
         <v>46295</v>
       </c>
@@ -8958,38 +8964,38 @@
       </c>
       <c r="AF54" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG54" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH54" s="4">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:34" ht="15" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="G55" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2">
         <v>5</v>
@@ -8998,28 +9004,26 @@
         <v>40</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M55" s="2"/>
-      <c r="N55" s="2" t="s">
-        <v>426</v>
-      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" s="2" t="s">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="R55" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="T55" s="2">
         <v>0</v>
@@ -9034,7 +9038,7 @@
         <v>45</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" s="2" t="s">
@@ -9043,7 +9047,9 @@
       <c r="AA55" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB55" s="2"/>
+      <c r="AB55" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="AC55" s="3">
         <v>46295</v>
       </c>
@@ -9057,38 +9063,38 @@
       </c>
       <c r="AF55" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG55" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>5</v>
-      </c>
-      <c r="AH55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-5</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="1:34" ht="15" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>207</v>
+        <v>75</v>
       </c>
       <c r="G56" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2">
         <v>5</v>
@@ -9097,27 +9103,29 @@
         <v>40</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
+      <c r="M56" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>419</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" s="2" t="s">
-        <v>184</v>
+        <v>307</v>
       </c>
       <c r="R56" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>470</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S56" s="2"/>
       <c r="T56" s="2">
         <v>0</v>
       </c>
@@ -9131,7 +9139,7 @@
         <v>45</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" s="2" t="s">
@@ -9141,10 +9149,10 @@
         <v>48</v>
       </c>
       <c r="AB56" s="2" t="s">
-        <v>186</v>
+        <v>309</v>
       </c>
       <c r="AC56" s="3">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="AD56" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -9162,32 +9170,32 @@
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
         <v>0</v>
       </c>
-      <c r="AH56" s="4" t="str">
+      <c r="AH56" s="4">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:34" ht="15" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G57" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
         <v>5</v>
@@ -9196,34 +9204,32 @@
         <v>40</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>426</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
       <c r="Q57" s="2" t="s">
-        <v>307</v>
+        <v>478</v>
       </c>
       <c r="R57" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>479</v>
+      </c>
       <c r="T57" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>45</v>
+        <v>480</v>
       </c>
       <c r="V57" s="2">
         <v>0</v>
@@ -9232,63 +9238,63 @@
         <v>45</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AA57" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB57" s="2" t="s">
-        <v>309</v>
+        <v>482</v>
       </c>
       <c r="AC57" s="3">
-        <v>46294</v>
+        <v>46303</v>
       </c>
       <c r="AD57" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE57" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF57" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG57" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>5</v>
-      </c>
-      <c r="AH57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-5</v>
+        <v/>
       </c>
     </row>
     <row r="58" spans="1:34" ht="15" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="G58" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2">
         <v>5</v>
@@ -9297,32 +9303,34 @@
         <v>40</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>96</v>
+        <v>390</v>
       </c>
       <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
+      <c r="N58" s="2" t="s">
+        <v>488</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
       <c r="Q58" s="2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="R58" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="T58" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>486</v>
+        <v>45</v>
       </c>
       <c r="V58" s="2">
         <v>0</v>
@@ -9331,63 +9339,63 @@
         <v>45</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" s="2" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AA58" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB58" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AC58" s="3">
-        <v>46303</v>
+        <v>46294</v>
       </c>
       <c r="AD58" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="AG58" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH58" s="4" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="4">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v/>
+        <v>-1</v>
       </c>
     </row>
     <row r="59" spans="1:34" ht="15" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>206</v>
+        <v>130</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="G59" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>5</v>
@@ -9396,34 +9404,32 @@
         <v>40</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>390</v>
+        <v>96</v>
       </c>
       <c r="M59" s="2"/>
-      <c r="N59" s="2" t="s">
-        <v>494</v>
-      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
       <c r="Q59" s="2" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="R59" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="T59" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>45</v>
+        <v>499</v>
       </c>
       <c r="V59" s="2">
         <v>0</v>
@@ -9432,60 +9438,60 @@
         <v>45</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AA59" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB59" s="2" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="AC59" s="3">
-        <v>46294</v>
+        <v>46303</v>
       </c>
       <c r="AD59" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE59" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF59" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG59" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>1</v>
-      </c>
-      <c r="AH59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-1</v>
+        <v/>
       </c>
     </row>
     <row r="60" spans="1:34" ht="15" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
@@ -9497,10 +9503,10 @@
         <v>40</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>96</v>
@@ -9510,19 +9516,19 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
       <c r="Q60" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="R60" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="T60" s="2">
         <v>6</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="V60" s="2">
         <v>0</v>
@@ -9531,7 +9537,7 @@
         <v>45</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" s="2" t="s">
@@ -9541,7 +9547,7 @@
         <v>48</v>
       </c>
       <c r="AB60" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AC60" s="3">
         <v>46303</v>
@@ -9569,22 +9575,22 @@
     </row>
     <row r="61" spans="1:34" ht="15" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
@@ -9596,10 +9602,10 @@
         <v>40</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>96</v>
@@ -9609,19 +9615,19 @@
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
       <c r="Q61" s="2" t="s">
-        <v>484</v>
+        <v>339</v>
       </c>
       <c r="R61" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="T61" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="V61" s="2">
         <v>0</v>
@@ -9630,7 +9636,7 @@
         <v>45</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" s="2" t="s">
@@ -9640,18 +9646,18 @@
         <v>48</v>
       </c>
       <c r="AB61" s="2" t="s">
-        <v>488</v>
+        <v>343</v>
       </c>
       <c r="AC61" s="3">
         <v>46303</v>
       </c>
       <c r="AD61" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE61" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF61" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -9668,22 +9674,22 @@
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
@@ -9695,10 +9701,10 @@
         <v>40</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>96</v>
@@ -9708,19 +9714,19 @@
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
       <c r="Q62" s="2" t="s">
-        <v>339</v>
+        <v>522</v>
       </c>
       <c r="R62" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="T62" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="V62" s="2">
         <v>0</v>
@@ -9729,7 +9735,7 @@
         <v>45</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" s="2" t="s">
@@ -9739,7 +9745,7 @@
         <v>48</v>
       </c>
       <c r="AB62" s="2" t="s">
-        <v>343</v>
+        <v>526</v>
       </c>
       <c r="AC62" s="3">
         <v>46303</v>
@@ -9750,7 +9756,7 @@
       </c>
       <c r="AE62" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF62" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -9767,22 +9773,22 @@
     </row>
     <row r="63" spans="1:34" ht="15" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
@@ -9794,10 +9800,10 @@
         <v>40</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>96</v>
@@ -9807,19 +9813,19 @@
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
       <c r="Q63" s="2" t="s">
-        <v>528</v>
+        <v>156</v>
       </c>
       <c r="R63" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="T63" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="V63" s="2">
         <v>0</v>
@@ -9828,7 +9834,7 @@
         <v>45</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" s="2" t="s">
@@ -9838,18 +9844,18 @@
         <v>48</v>
       </c>
       <c r="AB63" s="2" t="s">
-        <v>532</v>
+        <v>158</v>
       </c>
       <c r="AC63" s="3">
         <v>46303</v>
       </c>
       <c r="AD63" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE63" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF63" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -9866,22 +9872,22 @@
     </row>
     <row r="64" spans="1:34" ht="15" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
@@ -9893,32 +9899,34 @@
         <v>40</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M64" s="2"/>
+      <c r="M64" s="2" t="s">
+        <v>540</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
       <c r="Q64" s="2" t="s">
-        <v>154</v>
+        <v>541</v>
       </c>
       <c r="R64" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="T64" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="V64" s="2">
         <v>0</v>
@@ -9927,7 +9935,7 @@
         <v>45</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" s="2" t="s">
@@ -9937,18 +9945,18 @@
         <v>48</v>
       </c>
       <c r="AB64" s="2" t="s">
-        <v>156</v>
+        <v>545</v>
       </c>
       <c r="AC64" s="3">
         <v>46303</v>
       </c>
       <c r="AD64" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE64" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF64" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -9965,22 +9973,22 @@
     </row>
     <row r="65" spans="1:34" ht="15" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
@@ -9992,34 +10000,32 @@
         <v>40</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M65" s="2" t="s">
-        <v>546</v>
-      </c>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
       <c r="Q65" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="R65" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="T65" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="V65" s="2">
         <v>0</v>
@@ -10028,7 +10034,7 @@
         <v>45</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" s="2" t="s">
@@ -10038,18 +10044,18 @@
         <v>48</v>
       </c>
       <c r="AB65" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AC65" s="3">
         <v>46303</v>
       </c>
       <c r="AD65" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE65" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF65" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -10066,22 +10072,22 @@
     </row>
     <row r="66" spans="1:34" ht="15" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
@@ -10093,10 +10099,10 @@
         <v>40</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>96</v>
@@ -10106,19 +10112,19 @@
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
       <c r="Q66" s="2" t="s">
-        <v>557</v>
+        <v>522</v>
       </c>
       <c r="R66" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="T66" s="2">
         <v>6</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="V66" s="2">
         <v>0</v>
@@ -10127,7 +10133,7 @@
         <v>45</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" s="2" t="s">
@@ -10137,7 +10143,7 @@
         <v>48</v>
       </c>
       <c r="AB66" s="2" t="s">
-        <v>561</v>
+        <v>526</v>
       </c>
       <c r="AC66" s="3">
         <v>46303</v>
@@ -10165,22 +10171,22 @@
     </row>
     <row r="67" spans="1:34" ht="15" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>62</v>
+        <v>209</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
@@ -10192,10 +10198,10 @@
         <v>40</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>96</v>
@@ -10205,19 +10211,19 @@
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
       <c r="Q67" s="2" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="R67" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="T67" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="V67" s="2">
         <v>0</v>
@@ -10226,7 +10232,7 @@
         <v>45</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" s="2" t="s">
@@ -10236,7 +10242,7 @@
         <v>48</v>
       </c>
       <c r="AB67" s="2" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="AC67" s="3">
         <v>46303</v>
@@ -10247,7 +10253,7 @@
       </c>
       <c r="AE67" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF67" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -10264,22 +10270,22 @@
     </row>
     <row r="68" spans="1:34" ht="15" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
@@ -10291,10 +10297,10 @@
         <v>40</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>96</v>
@@ -10304,19 +10310,19 @@
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
       <c r="Q68" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="R68" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="T68" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="V68" s="2">
         <v>0</v>
@@ -10325,7 +10331,7 @@
         <v>45</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" s="2" t="s">
@@ -10335,7 +10341,7 @@
         <v>48</v>
       </c>
       <c r="AB68" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="AC68" s="3">
         <v>46303</v>
@@ -10346,7 +10352,7 @@
       </c>
       <c r="AE68" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF68" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -10363,22 +10369,22 @@
     </row>
     <row r="69" spans="1:34" ht="15" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
@@ -10390,10 +10396,10 @@
         <v>40</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>96</v>
@@ -10403,19 +10409,19 @@
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
       <c r="Q69" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="R69" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T69" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="V69" s="2">
         <v>0</v>
@@ -10424,7 +10430,7 @@
         <v>45</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" s="2" t="s">
@@ -10434,7 +10440,7 @@
         <v>48</v>
       </c>
       <c r="AB69" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="AC69" s="3">
         <v>46303</v>
@@ -10445,7 +10451,7 @@
       </c>
       <c r="AE69" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF69" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -10462,22 +10468,22 @@
     </row>
     <row r="70" spans="1:34" ht="15" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
@@ -10489,10 +10495,10 @@
         <v>40</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>96</v>
@@ -10502,19 +10508,19 @@
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
       <c r="Q70" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="R70" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="T70" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U70" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="V70" s="2">
         <v>0</v>
@@ -10523,7 +10529,7 @@
         <v>45</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" s="2" t="s">
@@ -10533,18 +10539,18 @@
         <v>48</v>
       </c>
       <c r="AB70" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="AC70" s="3">
         <v>46303</v>
       </c>
       <c r="AD70" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE70" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF70" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -10561,22 +10567,22 @@
     </row>
     <row r="71" spans="1:34" ht="15" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
@@ -10588,10 +10594,10 @@
         <v>40</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>96</v>
@@ -10601,19 +10607,19 @@
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" s="2" t="s">
-        <v>547</v>
+        <v>601</v>
       </c>
       <c r="R71" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="T71" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U71" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="V71" s="2">
         <v>0</v>
@@ -10622,7 +10628,7 @@
         <v>45</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" s="2" t="s">
@@ -10632,18 +10638,18 @@
         <v>48</v>
       </c>
       <c r="AB71" s="2" t="s">
-        <v>551</v>
+        <v>605</v>
       </c>
       <c r="AC71" s="3">
         <v>46303</v>
       </c>
       <c r="AD71" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE71" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF71" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
@@ -10660,59 +10666,63 @@
     </row>
     <row r="72" spans="1:34" ht="15" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>40</v>
+        <v>609</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
+      <c r="M72" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>449</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
       <c r="Q72" s="2" t="s">
-        <v>607</v>
+        <v>156</v>
       </c>
       <c r="R72" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="T72" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U72" s="2" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="V72" s="2">
         <v>0</v>
@@ -10721,7 +10731,7 @@
         <v>45</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" s="2" t="s">
@@ -10731,91 +10741,93 @@
         <v>48</v>
       </c>
       <c r="AB72" s="2" t="s">
-        <v>611</v>
+        <v>158</v>
       </c>
       <c r="AC72" s="3">
         <v>46303</v>
       </c>
       <c r="AD72" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE72" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF72" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="AG72" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH72" s="4" t="str">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="4">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v/>
+        <v>-5</v>
       </c>
     </row>
     <row r="73" spans="1:34" ht="15" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>74</v>
+        <v>619</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>75</v>
+        <v>620</v>
       </c>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H73" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>615</v>
+        <v>40</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>618</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>390</v>
+      </c>
       <c r="Q73" s="2" t="s">
-        <v>154</v>
+        <v>427</v>
       </c>
       <c r="R73" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="T73" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U73" s="2" t="s">
-        <v>620</v>
+        <v>45</v>
       </c>
       <c r="V73" s="2">
         <v>0</v>
@@ -10823,61 +10835,61 @@
       <c r="W73" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="X73" s="2" t="s">
-        <v>621</v>
+      <c r="X73" s="2">
+        <v>8584101831</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" s="2" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AA73" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB73" s="2" t="s">
-        <v>156</v>
+        <v>429</v>
       </c>
       <c r="AC73" s="3">
-        <v>46303</v>
+        <v>46309</v>
       </c>
       <c r="AD73" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE73" s="4">
         <f>PlannerTasks[[#This Row],[ChecklistItemCount]]-PlannerTasks[[#This Row],[ChecklistDone]]</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF73" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"No",IF(DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))&lt;TODAY(),"Yes","No"))</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="AG73" s="4">
         <f ca="1">IF(PlannerTasks[[#This Row],[IsOverdue]]="Yes",TODAY()-DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10)),0)</f>
-        <v>5</v>
-      </c>
-      <c r="AH73" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="4" t="str">
         <f ca="1">IF(OR(PlannerTasks[[#This Row],[DueDateTime]]="",PlannerTasks[[#This Row],[PercentComplete]]=100),"",DATEVALUE(LEFT(PlannerTasks[[#This Row],[DueDateTime]],10))-TODAY())</f>
-        <v>-5</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="1:34" ht="15" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G74" s="2">
         <v>100</v>
@@ -10889,10 +10901,10 @@
         <v>40</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>43</v>
@@ -10900,7 +10912,7 @@
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>43</v>
@@ -10925,7 +10937,7 @@
         <v>45</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" s="2" t="s">
@@ -10963,22 +10975,22 @@
     </row>
     <row r="75" spans="1:34" ht="15" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G75" s="2">
         <v>100</v>
@@ -10990,32 +11002,32 @@
         <v>40</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>400</v>
+        <v>623</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="R75" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="T75" s="2">
         <v>0</v>
@@ -11030,7 +11042,7 @@
         <v>45</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" s="2" t="s">
@@ -11040,7 +11052,7 @@
         <v>48</v>
       </c>
       <c r="AB75" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="AC75" s="3">
         <v>46303</v>
@@ -11068,22 +11080,22 @@
     </row>
     <row r="76" spans="1:34" ht="15" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G76" s="2">
         <v>100</v>
@@ -11095,26 +11107,26 @@
         <v>40</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P76" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R76" s="2" t="b">
         <v>0</v>
@@ -11133,7 +11145,7 @@
         <v>45</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" s="2" t="s">
@@ -11143,7 +11155,7 @@
         <v>48</v>
       </c>
       <c r="AB76" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC76" s="3">
         <v>46303</v>
@@ -11171,22 +11183,22 @@
     </row>
     <row r="77" spans="1:34" ht="15" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G77" s="2">
         <v>100</v>
@@ -11195,29 +11207,29 @@
         <v>1</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="R77" s="2" t="b">
         <v>0</v>
@@ -11236,20 +11248,20 @@
         <v>45</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AA77" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB77" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AC77" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AD77" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -11274,22 +11286,22 @@
     </row>
     <row r="78" spans="1:34" ht="15" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G78" s="2">
         <v>100</v>
@@ -11301,49 +11313,49 @@
         <v>40</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R78" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="T78" s="2">
         <v>2</v>
       </c>
       <c r="U78" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="V78" s="2">
         <v>3</v>
       </c>
       <c r="W78" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" s="2" t="s">
@@ -11353,7 +11365,7 @@
         <v>48</v>
       </c>
       <c r="AB78" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC78" s="3">
         <v>46296</v>
@@ -11381,22 +11393,22 @@
     </row>
     <row r="79" spans="1:34" ht="15" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G79" s="2">
         <v>100</v>
@@ -11405,13 +11417,13 @@
         <v>3</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>390</v>
@@ -11419,19 +11431,19 @@
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R79" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="T79" s="2">
         <v>0</v>
@@ -11446,7 +11458,7 @@
         <v>45</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" s="2" t="s">
@@ -11456,7 +11468,7 @@
         <v>48</v>
       </c>
       <c r="AB79" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC79" s="3">
         <v>46295</v>
@@ -11484,22 +11496,22 @@
     </row>
     <row r="80" spans="1:34" ht="15" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G80" s="2">
         <v>100</v>
@@ -11508,35 +11520,35 @@
         <v>3</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R80" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="T80" s="2">
         <v>0</v>
@@ -11548,10 +11560,10 @@
         <v>4</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" s="2" t="s">
@@ -11561,7 +11573,7 @@
         <v>48</v>
       </c>
       <c r="AB80" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC80" s="3">
         <v>46303</v>
@@ -11589,22 +11601,22 @@
     </row>
     <row r="81" spans="1:34" ht="15" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G81" s="2">
         <v>100</v>
@@ -11616,10 +11628,10 @@
         <v>40</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>390</v>
@@ -11627,7 +11639,7 @@
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>390</v>
@@ -11643,7 +11655,7 @@
         <v>2</v>
       </c>
       <c r="U81" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="V81" s="2">
         <v>0</v>
@@ -11652,7 +11664,7 @@
         <v>45</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" s="2" t="s">
@@ -11688,22 +11700,22 @@
     </row>
     <row r="82" spans="1:34" ht="15" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G82" s="2">
         <v>100</v>
@@ -11715,10 +11727,10 @@
         <v>40</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>43</v>
@@ -11726,7 +11738,7 @@
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="P82" s="2" t="s">
         <v>43</v>
@@ -11751,7 +11763,7 @@
         <v>45</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" s="2" t="s">
@@ -11789,22 +11801,22 @@
     </row>
     <row r="83" spans="1:34" ht="15" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G83" s="2">
         <v>100</v>
@@ -11816,10 +11828,10 @@
         <v>40</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>43</v>
@@ -11827,13 +11839,13 @@
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="P83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R83" s="2" t="b">
         <v>0</v>
@@ -11852,7 +11864,7 @@
         <v>45</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" s="2" t="s">
@@ -11862,7 +11874,7 @@
         <v>48</v>
       </c>
       <c r="AB83" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AC83" s="3">
         <v>46307</v>
@@ -11890,22 +11902,22 @@
     </row>
     <row r="84" spans="1:34" ht="15" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G84" s="2">
         <v>100</v>
@@ -11917,10 +11929,10 @@
         <v>40</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>43</v>
@@ -11928,13 +11940,13 @@
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="P84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R84" s="2" t="b">
         <v>0</v>
@@ -11953,7 +11965,7 @@
         <v>45</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" s="2" t="s">
@@ -11963,7 +11975,7 @@
         <v>48</v>
       </c>
       <c r="AB84" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AC84" s="3">
         <v>46303</v>
@@ -11991,22 +12003,22 @@
     </row>
     <row r="85" spans="1:34" ht="15" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G85" s="2">
         <v>100</v>
@@ -12018,10 +12030,10 @@
         <v>40</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>43</v>
@@ -12029,13 +12041,13 @@
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="P85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R85" s="2" t="b">
         <v>0</v>
@@ -12054,7 +12066,7 @@
         <v>45</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" s="2" t="s">
@@ -12064,7 +12076,7 @@
         <v>48</v>
       </c>
       <c r="AB85" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AC85" s="3">
         <v>46304</v>
@@ -12092,22 +12104,22 @@
     </row>
     <row r="86" spans="1:34" ht="15" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G86" s="2">
         <v>100</v>
@@ -12119,10 +12131,10 @@
         <v>40</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>43</v>
@@ -12130,7 +12142,7 @@
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="P86" s="2" t="s">
         <v>43</v>
@@ -12155,7 +12167,7 @@
         <v>45</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" s="2" t="s">
@@ -12193,22 +12205,22 @@
     </row>
     <row r="87" spans="1:34" ht="15" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G87" s="2">
         <v>100</v>
@@ -12220,34 +12232,34 @@
         <v>40</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>400</v>
+        <v>623</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="P87" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R87" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="T87" s="2">
         <v>0</v>
@@ -12262,7 +12274,7 @@
         <v>45</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" s="2" t="s">
@@ -12272,7 +12284,7 @@
         <v>48</v>
       </c>
       <c r="AB87" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC87" s="3">
         <v>46296</v>
@@ -12300,22 +12312,22 @@
     </row>
     <row r="88" spans="1:34" ht="15" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G88" s="2">
         <v>100</v>
@@ -12327,26 +12339,26 @@
         <v>40</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="P88" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="R88" s="2" t="b">
         <v>0</v>
@@ -12365,7 +12377,7 @@
         <v>45</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" s="2" t="s">
@@ -12375,7 +12387,7 @@
         <v>48</v>
       </c>
       <c r="AB88" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="AC88" s="3">
         <v>46304</v>
@@ -12403,22 +12415,22 @@
     </row>
     <row r="89" spans="1:34" ht="15" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G89" s="2">
         <v>100</v>
@@ -12430,10 +12442,10 @@
         <v>40</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>390</v>
@@ -12441,7 +12453,7 @@
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="P89" s="2" t="s">
         <v>390</v>
@@ -12466,7 +12478,7 @@
         <v>45</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" s="2" t="s">
@@ -12504,22 +12516,22 @@
     </row>
     <row r="90" spans="1:34" ht="15" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G90" s="2">
         <v>100</v>
@@ -12531,10 +12543,10 @@
         <v>40</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>43</v>
@@ -12542,13 +12554,13 @@
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="P90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R90" s="2" t="b">
         <v>0</v>
@@ -12567,20 +12579,20 @@
         <v>45</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AA90" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB90" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AC90" s="3" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AD90" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -12605,22 +12617,22 @@
     </row>
     <row r="91" spans="1:34" ht="15" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G91" s="2">
         <v>100</v>
@@ -12632,10 +12644,10 @@
         <v>40</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>43</v>
@@ -12643,7 +12655,7 @@
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="P91" s="2" t="s">
         <v>43</v>
@@ -12659,7 +12671,7 @@
         <v>2</v>
       </c>
       <c r="U91" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="V91" s="2">
         <v>0</v>
@@ -12668,11 +12680,11 @@
         <v>45</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AA91" s="2" t="s">
         <v>48</v>
@@ -12681,7 +12693,7 @@
         <v>80</v>
       </c>
       <c r="AC91" s="3" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AD91" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -12706,22 +12718,22 @@
     </row>
     <row r="92" spans="1:34" ht="15" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G92" s="2">
         <v>100</v>
@@ -12730,31 +12742,31 @@
         <v>1</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R92" s="2" t="b">
         <v>0</v>
@@ -12764,16 +12776,16 @@
         <v>1</v>
       </c>
       <c r="U92" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="V92" s="2">
         <v>1</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" s="2" t="s">
@@ -12783,7 +12795,7 @@
         <v>48</v>
       </c>
       <c r="AB92" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AC92" s="3">
         <v>46302</v>
@@ -12811,22 +12823,22 @@
     </row>
     <row r="93" spans="1:34" ht="15" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G93" s="2">
         <v>100</v>
@@ -12838,10 +12850,10 @@
         <v>40</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>96</v>
@@ -12849,34 +12861,34 @@
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="P93" s="2" t="s">
         <v>96</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="R93" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="T93" s="2">
         <v>2</v>
       </c>
       <c r="U93" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="V93" s="2">
         <v>1</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" s="2" t="s">
@@ -12886,7 +12898,7 @@
         <v>48</v>
       </c>
       <c r="AB93" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AC93" s="3">
         <v>46303</v>
@@ -12914,22 +12926,22 @@
     </row>
     <row r="94" spans="1:34" ht="15" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G94" s="2">
         <v>100</v>
@@ -12941,38 +12953,38 @@
         <v>40</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>96</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="P94" s="2" t="s">
         <v>96</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="R94" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="T94" s="2">
         <v>6</v>
       </c>
       <c r="U94" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="V94" s="2">
         <v>0</v>
@@ -12981,7 +12993,7 @@
         <v>45</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" s="2" t="s">
@@ -12991,7 +13003,7 @@
         <v>48</v>
       </c>
       <c r="AB94" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AC94" s="3">
         <v>46303</v>
@@ -13019,22 +13031,22 @@
     </row>
     <row r="95" spans="1:34" ht="15" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G95" s="2">
         <v>100</v>
@@ -13046,20 +13058,20 @@
         <v>40</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>96</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>96</v>
@@ -13071,13 +13083,13 @@
         <v>1</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="T95" s="2">
         <v>5</v>
       </c>
       <c r="U95" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="V95" s="2">
         <v>0</v>
@@ -13086,7 +13098,7 @@
         <v>45</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" s="2" t="s">
@@ -13124,22 +13136,22 @@
     </row>
     <row r="96" spans="1:34" ht="15" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G96" s="2">
         <v>100</v>
@@ -13151,10 +13163,10 @@
         <v>40</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>390</v>
@@ -13162,13 +13174,13 @@
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="P96" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R96" s="2" t="b">
         <v>0</v>
@@ -13187,7 +13199,7 @@
         <v>45</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" s="2" t="s">
@@ -13197,7 +13209,7 @@
         <v>48</v>
       </c>
       <c r="AB96" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AC96" s="3">
         <v>46303</v>
@@ -13225,22 +13237,22 @@
     </row>
     <row r="97" spans="1:34" ht="15" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G97" s="2">
         <v>100</v>
@@ -13252,26 +13264,26 @@
         <v>40</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R97" s="2" t="b">
         <v>0</v>
@@ -13290,7 +13302,7 @@
         <v>45</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" s="2" t="s">
@@ -13300,7 +13312,7 @@
         <v>48</v>
       </c>
       <c r="AB97" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC97" s="3">
         <v>46300</v>
@@ -13328,22 +13340,22 @@
     </row>
     <row r="98" spans="1:34" ht="15" customHeight="1">
       <c r="A98" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G98" s="2">
         <v>100</v>
@@ -13355,32 +13367,32 @@
         <v>40</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>400</v>
+        <v>623</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="P98" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R98" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="T98" s="2">
         <v>0</v>
@@ -13395,7 +13407,7 @@
         <v>45</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" s="2" t="s">
@@ -13405,7 +13417,7 @@
         <v>48</v>
       </c>
       <c r="AB98" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC98" s="3">
         <v>46295</v>
@@ -13433,22 +13445,22 @@
     </row>
     <row r="99" spans="1:34" ht="15" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G99" s="2">
         <v>100</v>
@@ -13460,10 +13472,10 @@
         <v>40</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>43</v>
@@ -13471,7 +13483,7 @@
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
       <c r="O99" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="P99" s="2" t="s">
         <v>43</v>
@@ -13496,7 +13508,7 @@
         <v>45</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" s="2" t="s">
@@ -13534,22 +13546,22 @@
     </row>
     <row r="100" spans="1:34" ht="15" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G100" s="2">
         <v>100</v>
@@ -13558,23 +13570,23 @@
         <v>1</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="M100" s="2"/>
       <c r="N100" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="P100" s="2" t="s">
         <v>390</v>
@@ -13586,7 +13598,7 @@
         <v>1</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="T100" s="2">
         <v>0</v>
@@ -13601,7 +13613,7 @@
         <v>45</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" s="2" t="s">
@@ -13639,22 +13651,22 @@
     </row>
     <row r="101" spans="1:34" ht="15" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G101" s="2">
         <v>100</v>
@@ -13666,10 +13678,10 @@
         <v>40</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>43</v>
@@ -13677,7 +13689,7 @@
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="P101" s="2" t="s">
         <v>43</v>
@@ -13702,7 +13714,7 @@
         <v>45</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" s="2" t="s">
@@ -13740,22 +13752,22 @@
     </row>
     <row r="102" spans="1:34" ht="15" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G102" s="2">
         <v>100</v>
@@ -13767,38 +13779,38 @@
         <v>40</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="P102" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R102" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="T102" s="2">
         <v>9</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="V102" s="2">
         <v>0</v>
@@ -13807,7 +13819,7 @@
         <v>45</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" s="2" t="s">
@@ -13817,7 +13829,7 @@
         <v>48</v>
       </c>
       <c r="AB102" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC102" s="3">
         <v>46302</v>
@@ -13845,22 +13857,22 @@
     </row>
     <row r="103" spans="1:34" ht="15" customHeight="1">
       <c r="A103" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G103" s="2">
         <v>100</v>
@@ -13869,23 +13881,23 @@
         <v>1</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="P103" s="2" t="s">
         <v>390</v>
@@ -13910,7 +13922,7 @@
         <v>45</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" s="2" t="s">
@@ -13946,22 +13958,22 @@
     </row>
     <row r="104" spans="1:34" ht="15" customHeight="1">
       <c r="A104" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G104" s="2">
         <v>100</v>
@@ -13973,26 +13985,26 @@
         <v>40</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="P104" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R104" s="2" t="b">
         <v>0</v>
@@ -14011,7 +14023,7 @@
         <v>45</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" s="2" t="s">
@@ -14021,7 +14033,7 @@
         <v>48</v>
       </c>
       <c r="AB104" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AC104" s="3">
         <v>46302</v>
@@ -14049,22 +14061,22 @@
     </row>
     <row r="105" spans="1:34" ht="15" customHeight="1">
       <c r="A105" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G105" s="2">
         <v>100</v>
@@ -14073,35 +14085,35 @@
         <v>1</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>400</v>
+        <v>623</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="P105" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="R105" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S105" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="T105" s="2">
         <v>0</v>
@@ -14116,7 +14128,7 @@
         <v>45</v>
       </c>
       <c r="X105" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" s="2" t="s">
@@ -14126,7 +14138,7 @@
         <v>48</v>
       </c>
       <c r="AB105" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="AC105" s="3">
         <v>46300</v>
@@ -14154,22 +14166,22 @@
     </row>
     <row r="106" spans="1:34" ht="15" customHeight="1">
       <c r="A106" s="2" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G106" s="2">
         <v>100</v>
@@ -14181,10 +14193,10 @@
         <v>40</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>43</v>
@@ -14192,7 +14204,7 @@
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="P106" s="2" t="s">
         <v>43</v>
@@ -14217,7 +14229,7 @@
         <v>45</v>
       </c>
       <c r="X106" s="2" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" s="2" t="s">
@@ -14253,22 +14265,22 @@
     </row>
     <row r="107" spans="1:34" ht="15" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G107" s="2">
         <v>100</v>
@@ -14280,10 +14292,10 @@
         <v>40</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>43</v>
@@ -14291,7 +14303,7 @@
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="P107" s="2" t="s">
         <v>43</v>
@@ -14316,18 +14328,18 @@
         <v>45</v>
       </c>
       <c r="X107" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AA107" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AB107" s="2"/>
       <c r="AC107" s="3" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AD107" s="4">
         <f>(LEN(PlannerTasks[[#This Row],[ChecklistSummary]])-LEN(SUBSTITUTE(PlannerTasks[[#This Row],[ChecklistSummary]],"""isChecked"":true","")))/LEN("""isChecked"":true")</f>
@@ -14352,22 +14364,22 @@
     </row>
     <row r="108" spans="1:34" ht="15" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G108" s="2">
         <v>100</v>
@@ -14379,20 +14391,20 @@
         <v>40</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="P108" s="2" t="s">
         <v>43</v>
@@ -14417,7 +14429,7 @@
         <v>45</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" s="2" t="s">
@@ -14453,22 +14465,22 @@
     </row>
     <row r="109" spans="1:34" ht="15" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G109" s="2">
         <v>100</v>
@@ -14480,32 +14492,32 @@
         <v>40</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>96</v>
       </c>
       <c r="M109" s="2"/>
       <c r="N109" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="P109" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R109" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S109" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="T109" s="2">
         <v>0</v>
@@ -14530,7 +14542,7 @@
         <v>48</v>
       </c>
       <c r="AB109" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC109" s="3">
         <v>46303</v>
@@ -14558,22 +14570,22 @@
     </row>
     <row r="110" spans="1:34" ht="15" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G110" s="2">
         <v>100</v>
@@ -14585,32 +14597,32 @@
         <v>40</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>96</v>
       </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="P110" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R110" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="T110" s="2">
         <v>0</v>
@@ -14635,7 +14647,7 @@
         <v>48</v>
       </c>
       <c r="AB110" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AC110" s="3">
         <v>46303</v>
@@ -14663,22 +14675,22 @@
     </row>
     <row r="111" spans="1:34" ht="15" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G111" s="2">
         <v>100</v>
@@ -14690,26 +14702,26 @@
         <v>40</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M111" s="2"/>
       <c r="N111" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="P111" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R111" s="2" t="b">
         <v>0</v>
@@ -14728,7 +14740,7 @@
         <v>45</v>
       </c>
       <c r="X111" s="2" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" s="2" t="s">
@@ -14738,7 +14750,7 @@
         <v>48</v>
       </c>
       <c r="AB111" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AC111" s="3">
         <v>46300</v>
@@ -14766,22 +14778,22 @@
     </row>
     <row r="112" spans="1:34" ht="15" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G112" s="2">
         <v>100</v>
@@ -14793,26 +14805,26 @@
         <v>40</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M112" s="2"/>
       <c r="N112" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="P112" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="R112" s="2" t="b">
         <v>0</v>
@@ -14831,7 +14843,7 @@
         <v>45</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" s="2" t="s">
@@ -14841,7 +14853,7 @@
         <v>48</v>
       </c>
       <c r="AB112" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="AC112" s="3">
         <v>46300</v>
@@ -14869,22 +14881,22 @@
     </row>
     <row r="113" spans="1:34" ht="15" customHeight="1">
       <c r="A113" s="2" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G113" s="2">
         <v>100</v>
@@ -14896,26 +14908,26 @@
         <v>40</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="P113" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R113" s="2" t="b">
         <v>0</v>
@@ -14934,7 +14946,7 @@
         <v>45</v>
       </c>
       <c r="X113" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" s="2" t="s">
@@ -14944,7 +14956,7 @@
         <v>48</v>
       </c>
       <c r="AB113" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AC113" s="3">
         <v>46297</v>
@@ -14972,22 +14984,22 @@
     </row>
     <row r="114" spans="1:34" ht="15" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G114" s="2">
         <v>100</v>
@@ -14999,26 +15011,26 @@
         <v>40</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M114" s="2"/>
       <c r="N114" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="P114" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R114" s="2" t="b">
         <v>0</v>
@@ -15037,7 +15049,7 @@
         <v>45</v>
       </c>
       <c r="X114" s="2" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" s="2" t="s">
@@ -15047,7 +15059,7 @@
         <v>48</v>
       </c>
       <c r="AB114" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AC114" s="3">
         <v>46297</v>
@@ -15075,22 +15087,22 @@
     </row>
     <row r="115" spans="1:34" ht="15" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G115" s="2">
         <v>100</v>
@@ -15102,10 +15114,10 @@
         <v>40</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>390</v>
@@ -15113,7 +15125,7 @@
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="P115" s="2" t="s">
         <v>390</v>
@@ -15125,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="T115" s="2">
         <v>0</v>
@@ -15140,7 +15152,7 @@
         <v>45</v>
       </c>
       <c r="X115" s="2" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" s="2" t="s">
@@ -15178,22 +15190,22 @@
     </row>
     <row r="116" spans="1:34" ht="15" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G116" s="2">
         <v>100</v>
@@ -15205,22 +15217,22 @@
         <v>40</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="P116" s="2" t="s">
         <v>390</v>
@@ -15232,7 +15244,7 @@
         <v>1</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="T116" s="2">
         <v>0</v>
@@ -15247,7 +15259,7 @@
         <v>45</v>
       </c>
       <c r="X116" s="2" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" s="2" t="s">
@@ -15285,22 +15297,22 @@
     </row>
     <row r="117" spans="1:34" ht="15" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="G117" s="2">
         <v>100</v>
@@ -15312,26 +15324,26 @@
         <v>40</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>390</v>
       </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="P117" s="2" t="s">
         <v>390</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R117" s="2" t="b">
         <v>0</v>
@@ -15350,7 +15362,7 @@
         <v>45</v>
       </c>
       <c r="X117" s="2" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" s="2" t="s">
@@ -15360,7 +15372,7 @@
         <v>48</v>
       </c>
       <c r="AB117" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AC117" s="3">
         <v>46296</v>
